--- a/MVP.xlsx
+++ b/MVP.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My Folder\IPL 2026 mock auction\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My Folder\IPL 2026 mock auction\ipl2026mockauction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3BDFEC0F-107D-437D-8C14-74D411890CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C5BAE55-4D5C-4D00-BF69-8AA22D2A0E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A6AE73A8-A285-41E1-A7E9-4E025B8992C0}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="85">
   <si>
     <t>Player</t>
   </si>
@@ -215,6 +215,81 @@
   <si>
     <t>Eshan Malinga</t>
   </si>
+  <si>
+    <t>Nandre Burger</t>
+  </si>
+  <si>
+    <t>RR</t>
+  </si>
+  <si>
+    <t>Vaibhav Sooryavanshi</t>
+  </si>
+  <si>
+    <t>Jofra Archer</t>
+  </si>
+  <si>
+    <t>Jamie Overton</t>
+  </si>
+  <si>
+    <t>CSK</t>
+  </si>
+  <si>
+    <t>Ravindra Jadeja</t>
+  </si>
+  <si>
+    <t>Kartik Sharma</t>
+  </si>
+  <si>
+    <t>Sandeep Sharma</t>
+  </si>
+  <si>
+    <t>Yashasvi Jaiswal</t>
+  </si>
+  <si>
+    <t>Sarfaraz Khan</t>
+  </si>
+  <si>
+    <t>Anshul Kamboj</t>
+  </si>
+  <si>
+    <t>Brijesh Sharma</t>
+  </si>
+  <si>
+    <t>Dhruv Jurel</t>
+  </si>
+  <si>
+    <t>Ravi Bishnoi</t>
+  </si>
+  <si>
+    <t>Shivam Dube</t>
+  </si>
+  <si>
+    <t>Riyan Parag</t>
+  </si>
+  <si>
+    <t>Khaleel Ahmed</t>
+  </si>
+  <si>
+    <t>Sanju Samson</t>
+  </si>
+  <si>
+    <t>Shimron Hetmyer</t>
+  </si>
+  <si>
+    <t>Ayush Mhatre</t>
+  </si>
+  <si>
+    <t>Ruturaj Gaikwad</t>
+  </si>
+  <si>
+    <t>Matthew Short</t>
+  </si>
+  <si>
+    <t>Noor Ahmad</t>
+  </si>
+  <si>
+    <t>Matt Henry</t>
+  </si>
 </sst>
 </file>
 
@@ -334,6 +409,15 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -341,15 +425,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3316,6 +3391,4382 @@
       <xdr:spPr bwMode="auto">
         <a:xfrm>
           <a:off x="0" y="35844480"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="49" name="Picture 48" descr="Jacob Duffy, player portrait">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DA3CD0A-20AD-7DE5-CD9E-3CA97C1A305A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="365760"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="50" name="Picture 49" descr="Ishan Kishan player page headshot cutout 2021">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC6E6F47-AF07-0F6C-6160-58F7DFE58D5B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="914400"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="51" name="Picture 50" descr="Shardul Thakur player page headshot cutout, 2021">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADB9D4CB-E979-17A1-C30C-0951FEF357F8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="1463040"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="52" name="Picture 51" descr="Rohit Sharma, player page headshot cutout, 2024">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8EFB12D-57A4-CD2A-5E0B-1C01FDA0804F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="2011680"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="53" name="Picture 52" descr="Ryan Rickelton, player page headshot cutout 2023">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49644508-4D3A-DFBF-EFB5-8AB8CF2C21F7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="2560320"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="54" name="Picture 53" descr="Devdutt Padikkal player page headshot cutout, 2021">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5EC21D8B-23C0-5A61-5412-4C8BE0D6AD1E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="3108960"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="55" name="Picture 54" descr="Nandre Burger, player portrait">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId96"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35D4AF9C-BE03-33DB-24EC-B2FB6C0A25A7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId97" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="3657600"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="56" name="Picture 55" descr="Aniket Verma, player portrait">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A149144-E34A-5795-4506-75AAE27A0950}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="4206240"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="57" name="Picture 56" descr="Vaibhav Sooryavanshi, player portrait">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId98"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE78AE7B-F347-706D-5F5D-AA05BD536D6C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId99" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="4754880"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="58" name="Picture 57" descr="Jofra Archer cutout">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId100"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C659CEC-FE65-8663-B0EA-0DD4F061F8E3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId101" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="5303520"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="59" name="Picture 58" descr="V Kohli headshot">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16D568E0-ADFC-0E2C-9306-171E74EB24E8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="5852160"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="60" name="Picture 59" descr="Jamie Overton player page headshot cutout, 2021">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId102"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D589C4B-3A2D-3B36-969C-84718007B75F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId103" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="6400800"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="61" name="Picture 60" descr="Kartik Tyagi, player page headshot cutout 2022">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId17"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66ED9EDE-BEF5-0992-65DC-37DDFFBC1DD0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="6949440"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="62" name="Picture 61" descr="Romario Shepherd, player portrait">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59911949-A60D-26B6-2CFB-55FDC8916F95}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="7498080"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="63" name="Picture 62" descr="AM Rahane headshot">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId21"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A9FD94B-106E-6914-5289-9594DEFFE812}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="8046720"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1024" name="Picture 1023" descr="Finn Allen portrait">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId23"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CA55BF7-287A-B9DC-B75F-E59C8F0D5E88}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="8595360"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1025" name="Picture 1024" descr="RA Jadeja headshot">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId104"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5C35D96-AECA-A8C4-5D25-6492A69E60DE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId105" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="9144000"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1026" name="Picture 1025" descr="Jaydev Unadkat, player portrait">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId25"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2B8FE55-2772-5604-D96A-1E680129A7CA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="9692640"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1027" name="Picture 1026" descr="Suyash Sharma, player page headshot cutout 2023">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId27"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5613E57-3532-AAEF-2360-76E1894DFB7E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="10241280"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1028" name="Picture 1027" descr="Angkrish Raghuvanshi, player page headshot cutout 2022">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId29"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BF7E949-EF20-FF04-61F7-A8A0BF48EE29}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId30" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="10789920"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1029" name="Picture 1028" descr="Hardik Pandya, player portrait">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId31"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4EE9A30-10B3-B32A-F96C-411590B69E9F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="11338560"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1030" name="Picture 1029" descr="Bhuvneshwar Kumar, player portrait">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId33"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2AA73751-B891-61C1-086E-6D9173E2D2D1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId34" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="11887200"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1031" name="Picture 1030" descr="David Payne player page headshot cutout, 2021">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId35"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24BA6E12-79B9-6136-B32E-1F320424979D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId36" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="12435840"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1032" name="Picture 1031" descr="Jasprit Bumrah player page headshot cutout, 2021">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId37"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52F7D282-1462-72B6-EAE8-15AABA7ACF80}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId38" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="12984480"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1033" name="Picture 1032" descr="Vaibhav Arora, player portrait">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId39"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6A4B43A-C271-3269-E76E-B3D46B5E7B4B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId40" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="13533120"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1034" name="Picture 1033" descr="Sunil Narine player page headshot cutout, 2021">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId41"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F669D4B4-A305-F3CE-FF1C-ACE7190CC489}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId42" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="14081760"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1035" name="Picture 1034" descr="Rajat Patidar, player portrait">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId43"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1069743-E0A5-6820-A4E0-ABA0319ED95D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId44" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="14630400"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1036" name="Picture 1035" descr="Kartik Sharma, player portrait">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId106"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3D2A9A4-B5DB-95A2-4747-88DB0B1C67C6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId107" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="15179040"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1037" name="Picture 1036" descr="Sandeep Sharma player page headshot cutout, 2021">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId108"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54A300DA-3C4D-1345-05F4-EE8E8DF08F54}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId109" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="15727680"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1038" name="Picture 1037" descr="Harsh Dubey, player portrait">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId45"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32C56337-651E-46ED-4827-7B2A22C2CE63}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId46" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="16276320"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1039" name="Picture 1038" descr="Yashasvi Jaiswal, player page headshot cutout 2022">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId110"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{409D6A2F-E675-9C2C-3B87-63ACB3D1E553}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId111" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="16824960"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1040" name="Picture 1039" descr="Sarfaraz Khan, player portrait">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId112"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70A4E6B7-BA1F-4957-4D48-80A529526530}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId113" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="17373600"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1041" name="Picture 1040" descr="Trent Boult portrait">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId47"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73A19131-C306-8496-C516-CF506EB16AFA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId48" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="17922240"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1042" name="Picture 1041" descr="Anshul Kamboj, player page headshot cutout, 2024">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId114"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CD5F9C7-4F70-B8B2-39D6-0AB3E5D02993}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId115" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="18470880"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1059" name="AutoShape 35">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId116"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DAFB18A5-7A68-1585-C782-5B76E30E4245}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="19019520"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1043" name="Picture 1042" descr="Abhinandan Singh, player portrait">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId49"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0066729A-2ACD-A3D4-CBA7-D7F5B91FB7F8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId50" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="19568160"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>111</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1044" name="Picture 1043" descr="Suryakumar Yadav player page headshot cutout 2021">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId51"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE157E51-4F50-240E-BED9-44A8204C3929}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId52" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="20116800"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>113</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1045" name="Picture 1044" descr="Heinrich Klaasen player page headshot cutout, 2021">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId53"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9363ACBD-F110-FB4B-F866-DB1CD3F4EC3D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId54" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="20665440"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1046" name="Picture 1045" descr="Dhruv Jurel, player page headshot cutout 2022">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId117"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33CC88E7-4096-2E16-742C-5845DA049088}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId118" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="21214080"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1047" name="Picture 1046" descr="Tilak Varma, player page headshot cutout, 2024">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId55"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBE7B55B-FC5F-5DF3-2F95-6D877CE6D6B3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId56" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="21762720"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>122</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>123</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1048" name="Picture 1047" descr="Cameron Green player page headshot cutout, 2024">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId57"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9075E4C0-D7C6-DB8C-7741-373126FCF14A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId58" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="22311360"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1049" name="Picture 1048" descr="Ravi Bishnoi, player page headshot cutout 2022">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId119"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB48A29E-0161-FD30-D2DD-EB6E2DEB1474}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId120" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="22860000"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>128</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>129</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1050" name="Picture 1049" descr="Shivam Dube, player page headshot cutout, 2024">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId121"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ABF808C8-49B9-DF2A-C5C4-D3C520ADB86E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId122" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="23408640"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>131</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1051" name="Picture 1050" descr="Tim David, player page headshot cutout 2022">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId59"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BBF4481-1E8F-D02E-A6FA-6C1F9782195E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId60" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="23957280"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>134</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1052" name="Picture 1051" descr="Riyan Parag, player page headshot cutout 2023">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId123"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{220E2C2C-232D-1962-AF71-1DC8B3872462}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId124" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="24505920"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>137</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>138</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1053" name="Picture 1052" descr="Khaleel Ahmed player page headshot cutout, 2021">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId125"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D287C72-B847-A80F-D09C-F21B7649BA3E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId126" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="25054560"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>140</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>141</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1054" name="Picture 1053" descr="Blessing Muzarabani player page headshot cutout, 2021">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId61"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A20DD761-3E1B-9610-E9C9-7AC969262797}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId62" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="25603200"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>143</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>144</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1055" name="Picture 1054" descr="Rinku Singh, player page headshot cutout 2022">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId63"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{214009E9-0192-0062-9C75-1A1B0F4C1028}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId64" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="26151840"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>147</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1056" name="Picture 1055" descr="Varun Chakravarthy player page headshot cutout 2021">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId65"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9D4C31D-3C1A-380C-A6BF-357A8E225503}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId66" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="26700480"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>149</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>150</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1074" name="AutoShape 50">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId67"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C0E1371-8885-2167-F678-B4FAF4194FE5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="27249120"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>152</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>153</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1057" name="Picture 1056" descr="Naman Dhir, player page headshot cutout, 2024">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId68"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A708502F-FB80-9459-C5B0-3E2A7265C2BA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId69" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="27797760"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>155</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>156</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1060" name="Picture 1059" descr="Travis Head player page headshot cutout, 2021">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId70"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{100023F9-A1BD-C89E-7A91-BB151E0A56A1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId71" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="28346400"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>158</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>159</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1061" name="Picture 1060" descr="Anukul Roy, player page headshot cutout 2022">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId72"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5991B4AC-5EE9-83E6-F4C1-CAC545F0F69A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId73" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="28895040"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>161</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>162</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1062" name="Picture 1061" descr="Sanju Samson player page headshot cutout, 2021">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId127"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCA69782-CAD3-5660-657F-FDDE78EAF6FA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId128" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="29443680"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>164</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>165</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1063" name="Picture 1062" descr="AM Ghazanfar, player portrait">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId74"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D3D4D37-069D-9B1A-D141-A32247B375B0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId75" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="29992320"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>167</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>168</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1064" name="Picture 1063" descr="Phil Salt player, player page headshot cutout, 2024,">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId76"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D4D55FA-742D-F24C-1FC4-1BED5AD632E2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId77" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="30540960"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>170</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>171</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1065" name="Picture 1064" descr="Sherfane Rutherford player page headshot cutout, 2021">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId78"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{461CB35F-771C-1F5F-14A4-0305DC44E568}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId79" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="31089600"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>173</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>174</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1066" name="Picture 1065" descr="Shimron Hetmyer player page headshot cutout, 2021">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId129"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8F78770-729D-C967-541F-C09ADA1A54B6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId130" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="31638240"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>176</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>177</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1067" name="Picture 1066" descr="Krunal Pandya player page headshot cutout, 2021">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId80"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFA297C0-ABD4-543C-B12E-131F85EE0274}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId81" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="32186880"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>179</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>180</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1068" name="Picture 1067" descr="Jitesh Sharma, player page headshot cutout, 2024">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId82"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E08911A-BD59-834B-C0D4-A558F3790D78}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId83" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="32735520"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>182</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>183</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1069" name="Picture 1068" descr="Ayush Mhatre, player portrait">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId131"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAC3FF6F-DF46-8AC7-539D-56FC5A0D8D69}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId132" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="33284160"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>185</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>186</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1070" name="Picture 1069" descr="Harshal Patel, player page headshot cutout, 2024">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId84"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E1A1CFB-0FA5-FDFE-EC00-6B2835201D54}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId85" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="33832800"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>188</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>189</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1071" name="Picture 1070" descr="Ruturaj Gaikwad player page headshot cutout, 2021">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId133"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58E893B6-B490-1AEA-B631-448DE0E09D53}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId134" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="34381440"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>191</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>192</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1072" name="Picture 1071" descr="Mayank Markande, player page headshot cutout 2023">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId86"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B53FD558-1B8B-0310-7F7C-F2FFEA7F8AD6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId87" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="34930080"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>194</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>195</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1073" name="Picture 1072" descr="Abhishek Sharma, player page headshot cutout 2023">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId88"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EEA71763-BAAF-EE60-A3D1-D6A1B2C25E1E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId89" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="35478720"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>197</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>198</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1075" name="Picture 1074" descr="Ramandeep Singh, player portrait">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId90"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7FA33DD-0287-1F6B-6E54-CD8E76625937}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId91" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="36027360"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>200</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>201</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1076" name="Picture 1075" descr="Matthew Short, player page headshot cutout, 2024">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId135"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCC09C89-6E8D-F584-3F69-BDA595AE3033}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId136" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="36576000"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>203</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>204</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1077" name="Picture 1076" descr="Nitish Kumar Reddy, player portrait">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId92"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFE5EFE9-921C-8498-431B-10085E99D64A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId93" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="37124640"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>206</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>207</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1078" name="Picture 1077" descr="Eshan Malinga, player portrait">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId94"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3803909-F346-87EF-780C-A57A3D43C852}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId95" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="37673280"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>209</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>210</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1079" name="Picture 1078" descr="Noor Ahmad cutout">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId137"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F27ECE6-9EDD-BCA5-3970-1EB531B6D695}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId138" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="38221920"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>212</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>213</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1080" name="Picture 1079" descr="Matt Henry portrait">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId139"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C478455-5298-1F3E-05EB-015BDB39B0D6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId140" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="38770560"/>
           <a:ext cx="304800" cy="304800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3635,7 +8086,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EC68DE8-77DA-4286-A14C-3B94EF6E75DB}">
-  <dimension ref="A1:G145"/>
+  <dimension ref="A1:G214"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.6640625" customWidth="1"/>
@@ -3669,2068 +8120,3471 @@
       <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="13">
         <v>123.6</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="14">
         <v>123.6</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="14">
         <v>1</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="14">
         <v>0</v>
       </c>
-      <c r="G2" s="11">
+      <c r="G2" s="14">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-    </row>
-    <row r="4" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B3" s="12"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>2</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="10">
         <v>113.1</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="11">
         <v>113.1</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="11">
         <v>1</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="11">
         <v>80</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-    </row>
-    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B6" s="9"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>3</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="10">
         <v>100.8</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="11">
         <v>100.8</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="11">
         <v>1</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="11">
         <v>0</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-    </row>
-    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B9" s="9"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>4</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="10">
         <v>93.5</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="11">
         <v>93.5</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="11">
         <v>1</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="11">
         <v>78</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="7"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-    </row>
-    <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B12" s="9"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>5</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="10">
         <v>92.2</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="11">
         <v>92.2</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="11">
         <v>1</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="11">
         <v>81</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="7"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-    </row>
-    <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B15" s="9"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>6</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="13">
+      <c r="C17" s="10">
         <v>80.7</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="11">
         <v>80.7</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="11">
         <v>1</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="11">
         <v>61</v>
       </c>
-      <c r="G17" s="14" t="s">
+      <c r="G17" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="7"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-    </row>
-    <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B18" s="9"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>7</v>
       </c>
-      <c r="B20" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="13">
-        <v>65.599999999999994</v>
-      </c>
-      <c r="D20" s="14">
-        <v>65.599999999999994</v>
-      </c>
-      <c r="E20" s="14">
+      <c r="B20" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="10">
+        <v>71</v>
+      </c>
+      <c r="D20" s="11">
+        <v>71</v>
+      </c>
+      <c r="E20" s="11">
         <v>1</v>
       </c>
-      <c r="F20" s="14">
-        <v>43</v>
-      </c>
-      <c r="G20" s="14" t="s">
-        <v>11</v>
+      <c r="F20" s="11">
+        <v>0</v>
+      </c>
+      <c r="G20" s="11">
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="7"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-    </row>
-    <row r="22" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B21" s="9"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
+        <v>60</v>
+      </c>
+      <c r="B22" s="9"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>8</v>
       </c>
-      <c r="B23" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="13">
-        <v>52.5</v>
-      </c>
-      <c r="D23" s="14">
-        <v>52.5</v>
-      </c>
-      <c r="E23" s="14">
+      <c r="B23" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="10">
+        <v>65.599999999999994</v>
+      </c>
+      <c r="D23" s="11">
+        <v>65.599999999999994</v>
+      </c>
+      <c r="E23" s="11">
         <v>1</v>
       </c>
-      <c r="F23" s="14">
-        <v>69</v>
-      </c>
-      <c r="G23" s="14" t="s">
+      <c r="F23" s="11">
+        <v>43</v>
+      </c>
+      <c r="G23" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="7"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-    </row>
-    <row r="25" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B24" s="9"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B25" s="12"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
+        <v>17</v>
+      </c>
+      <c r="B25" s="9"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="6">
         <v>9</v>
       </c>
-      <c r="B26" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" s="13">
-        <v>52.1</v>
-      </c>
-      <c r="D26" s="14">
-        <v>52.1</v>
-      </c>
-      <c r="E26" s="14">
+      <c r="B26" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="10">
+        <v>64.099999999999994</v>
+      </c>
+      <c r="D26" s="11">
+        <v>64.099999999999994</v>
+      </c>
+      <c r="E26" s="11">
         <v>1</v>
       </c>
-      <c r="F26" s="14">
-        <v>0</v>
-      </c>
-      <c r="G26" s="14">
-        <v>1</v>
+      <c r="F26" s="11">
+        <v>52</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="7"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-    </row>
-    <row r="28" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B27" s="9"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B28" s="12"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
+        <v>62</v>
+      </c>
+      <c r="B28" s="9"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="6">
         <v>10</v>
       </c>
-      <c r="B29" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="13">
-        <v>49.5</v>
-      </c>
-      <c r="D29" s="14">
-        <v>49.5</v>
-      </c>
-      <c r="E29" s="14">
+      <c r="B29" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29" s="10">
+        <v>52.6</v>
+      </c>
+      <c r="D29" s="11">
+        <v>52.6</v>
+      </c>
+      <c r="E29" s="11">
         <v>1</v>
       </c>
-      <c r="F29" s="14">
+      <c r="F29" s="11">
         <v>0</v>
       </c>
-      <c r="G29" s="14">
-        <v>3</v>
+      <c r="G29" s="11">
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="7"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-    </row>
-    <row r="31" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B30" s="9"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B31" s="12"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
+        <v>63</v>
+      </c>
+      <c r="B31" s="9"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="6">
         <v>11</v>
       </c>
-      <c r="B32" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C32" s="13">
-        <v>47.5</v>
-      </c>
-      <c r="D32" s="14">
-        <v>47.5</v>
-      </c>
-      <c r="E32" s="14">
+      <c r="B32" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="10">
+        <v>52.5</v>
+      </c>
+      <c r="D32" s="11">
+        <v>52.5</v>
+      </c>
+      <c r="E32" s="11">
         <v>1</v>
       </c>
-      <c r="F32" s="14">
-        <v>67</v>
-      </c>
-      <c r="G32" s="14" t="s">
+      <c r="F32" s="11">
+        <v>69</v>
+      </c>
+      <c r="G32" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="7"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-    </row>
-    <row r="34" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B33" s="9"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B34" s="12"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
+        <v>18</v>
+      </c>
+      <c r="B34" s="9"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="6">
         <v>12</v>
       </c>
-      <c r="B35" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C35" s="13">
-        <v>46.3</v>
-      </c>
-      <c r="D35" s="14">
-        <v>46.3</v>
-      </c>
-      <c r="E35" s="14">
+      <c r="B35" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C35" s="10">
+        <v>52.4</v>
+      </c>
+      <c r="D35" s="11">
+        <v>52.4</v>
+      </c>
+      <c r="E35" s="11">
         <v>1</v>
       </c>
-      <c r="F35" s="14">
-        <v>37</v>
-      </c>
-      <c r="G35" s="14" t="s">
+      <c r="F35" s="11">
+        <v>43</v>
+      </c>
+      <c r="G35" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="7"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B37" s="12"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
+        <v>64</v>
+      </c>
+      <c r="B37" s="9"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="6">
         <v>13</v>
       </c>
-      <c r="B38" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="13">
-        <v>42.3</v>
-      </c>
-      <c r="D38" s="14">
-        <v>42.3</v>
-      </c>
-      <c r="E38" s="14">
+      <c r="B38" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="10">
+        <v>52.1</v>
+      </c>
+      <c r="D38" s="11">
+        <v>52.1</v>
+      </c>
+      <c r="E38" s="11">
         <v>1</v>
       </c>
-      <c r="F38" s="14">
-        <v>4</v>
-      </c>
-      <c r="G38" s="14">
+      <c r="F38" s="11">
+        <v>0</v>
+      </c>
+      <c r="G38" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="7"/>
-      <c r="B39" s="12"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-    </row>
-    <row r="40" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B39" s="9"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B40" s="12"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
+        <v>19</v>
+      </c>
+      <c r="B40" s="9"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="6">
         <v>14</v>
       </c>
-      <c r="B41" s="12" t="s">
+      <c r="B41" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C41" s="13">
-        <v>39.700000000000003</v>
-      </c>
-      <c r="D41" s="14">
-        <v>39.700000000000003</v>
-      </c>
-      <c r="E41" s="14">
+      <c r="C41" s="10">
+        <v>49.5</v>
+      </c>
+      <c r="D41" s="11">
+        <v>49.5</v>
+      </c>
+      <c r="E41" s="11">
         <v>1</v>
       </c>
-      <c r="F41" s="14">
+      <c r="F41" s="11">
         <v>0</v>
       </c>
-      <c r="G41" s="14">
-        <v>1</v>
+      <c r="G41" s="11">
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="7"/>
-      <c r="B42" s="12"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-    </row>
-    <row r="43" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B42" s="9"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B43" s="12"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
+        <v>21</v>
+      </c>
+      <c r="B43" s="9"/>
+      <c r="C43" s="10"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="6">
         <v>15</v>
       </c>
-      <c r="B44" s="12" t="s">
+      <c r="B44" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C44" s="13">
-        <v>39.200000000000003</v>
-      </c>
-      <c r="D44" s="14">
-        <v>39.200000000000003</v>
-      </c>
-      <c r="E44" s="14">
+      <c r="C44" s="10">
+        <v>47.5</v>
+      </c>
+      <c r="D44" s="11">
+        <v>47.5</v>
+      </c>
+      <c r="E44" s="11">
         <v>1</v>
       </c>
-      <c r="F44" s="14">
-        <v>51</v>
-      </c>
-      <c r="G44" s="14" t="s">
+      <c r="F44" s="11">
+        <v>67</v>
+      </c>
+      <c r="G44" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="7"/>
-      <c r="B45" s="12"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-    </row>
-    <row r="46" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B45" s="9"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B46" s="12"/>
-      <c r="C46" s="13"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
+        <v>22</v>
+      </c>
+      <c r="B46" s="9"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="6">
         <v>16</v>
       </c>
-      <c r="B47" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C47" s="13">
+      <c r="B47" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" s="10">
+        <v>46.3</v>
+      </c>
+      <c r="D47" s="11">
+        <v>46.3</v>
+      </c>
+      <c r="E47" s="11">
+        <v>1</v>
+      </c>
+      <c r="F47" s="11">
         <v>37</v>
       </c>
-      <c r="D47" s="14">
-        <v>37</v>
-      </c>
-      <c r="E47" s="14">
-        <v>1</v>
-      </c>
-      <c r="F47" s="14">
-        <v>18</v>
-      </c>
-      <c r="G47" s="14">
-        <v>1</v>
+      <c r="G47" s="11" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="7"/>
-      <c r="B48" s="12"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-    </row>
-    <row r="49" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B48" s="9"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B49" s="12"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
+        <v>23</v>
+      </c>
+      <c r="B49" s="9"/>
+      <c r="C49" s="10"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="11"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="6">
         <v>17</v>
       </c>
-      <c r="B50" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C50" s="13">
-        <v>35.9</v>
-      </c>
-      <c r="D50" s="14">
-        <v>35.9</v>
-      </c>
-      <c r="E50" s="14">
+      <c r="B50" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C50" s="10">
+        <v>45.7</v>
+      </c>
+      <c r="D50" s="11">
+        <v>45.7</v>
+      </c>
+      <c r="E50" s="11">
         <v>1</v>
       </c>
-      <c r="F50" s="14">
+      <c r="F50" s="11">
         <v>0</v>
       </c>
-      <c r="G50" s="14">
-        <v>1</v>
+      <c r="G50" s="11">
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="7"/>
-      <c r="B51" s="12"/>
-      <c r="C51" s="13"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-    </row>
-    <row r="52" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B51" s="9"/>
+      <c r="C51" s="10"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B52" s="12"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
+        <v>66</v>
+      </c>
+      <c r="B52" s="9"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="11"/>
+      <c r="E52" s="11"/>
+      <c r="F52" s="11"/>
+      <c r="G52" s="11"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="6">
         <v>18</v>
       </c>
-      <c r="B53" s="12" t="s">
+      <c r="B53" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C53" s="13">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="D53" s="14">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="E53" s="14">
+      <c r="C53" s="10">
+        <v>42.3</v>
+      </c>
+      <c r="D53" s="11">
+        <v>42.3</v>
+      </c>
+      <c r="E53" s="11">
         <v>1</v>
       </c>
-      <c r="F53" s="14">
-        <v>6</v>
-      </c>
-      <c r="G53" s="14">
-        <v>2</v>
+      <c r="F53" s="11">
+        <v>4</v>
+      </c>
+      <c r="G53" s="11">
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="7"/>
-      <c r="B54" s="12"/>
-      <c r="C54" s="13"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-    </row>
-    <row r="55" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B54" s="9"/>
+      <c r="C54" s="10"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="11"/>
+      <c r="F54" s="11"/>
+      <c r="G54" s="11"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B55" s="12"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
+        <v>24</v>
+      </c>
+      <c r="B55" s="9"/>
+      <c r="C55" s="10"/>
+      <c r="D55" s="11"/>
+      <c r="E55" s="11"/>
+      <c r="F55" s="11"/>
+      <c r="G55" s="11"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="6">
         <v>19</v>
       </c>
-      <c r="B56" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C56" s="13">
-        <v>31.9</v>
-      </c>
-      <c r="D56" s="14">
-        <v>31.9</v>
-      </c>
-      <c r="E56" s="14">
+      <c r="B56" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" s="10">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="D56" s="11">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="E56" s="11">
         <v>1</v>
       </c>
-      <c r="F56" s="14">
+      <c r="F56" s="11">
         <v>0</v>
       </c>
-      <c r="G56" s="14" t="s">
-        <v>11</v>
+      <c r="G56" s="11">
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="7"/>
-      <c r="B57" s="12"/>
-      <c r="C57" s="13"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-    </row>
-    <row r="58" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B57" s="9"/>
+      <c r="C57" s="10"/>
+      <c r="D57" s="11"/>
+      <c r="E57" s="11"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="11"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B58" s="12"/>
-      <c r="C58" s="13"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
+        <v>25</v>
+      </c>
+      <c r="B58" s="9"/>
+      <c r="C58" s="10"/>
+      <c r="D58" s="11"/>
+      <c r="E58" s="11"/>
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="6">
         <v>20</v>
       </c>
-      <c r="B59" s="12" t="s">
+      <c r="B59" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C59" s="13">
-        <v>31.7</v>
-      </c>
-      <c r="D59" s="14">
-        <v>31.7</v>
-      </c>
-      <c r="E59" s="14">
+      <c r="C59" s="10">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="D59" s="11">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="E59" s="11">
         <v>1</v>
       </c>
-      <c r="F59" s="14">
-        <v>0</v>
-      </c>
-      <c r="G59" s="14">
-        <v>1</v>
+      <c r="F59" s="11">
+        <v>51</v>
+      </c>
+      <c r="G59" s="11" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="7"/>
-      <c r="B60" s="12"/>
-      <c r="C60" s="13"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-    </row>
-    <row r="61" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B60" s="9"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="11"/>
+      <c r="E60" s="11"/>
+      <c r="F60" s="11"/>
+      <c r="G60" s="11"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B61" s="12"/>
-      <c r="C61" s="13"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
+        <v>26</v>
+      </c>
+      <c r="B61" s="9"/>
+      <c r="C61" s="10"/>
+      <c r="D61" s="11"/>
+      <c r="E61" s="11"/>
+      <c r="F61" s="11"/>
+      <c r="G61" s="11"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="6">
         <v>21</v>
       </c>
-      <c r="B62" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C62" s="13">
-        <v>31.4</v>
-      </c>
-      <c r="D62" s="14">
-        <v>31.4</v>
-      </c>
-      <c r="E62" s="14">
+      <c r="B62" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="10">
+        <v>37</v>
+      </c>
+      <c r="D62" s="11">
+        <v>37</v>
+      </c>
+      <c r="E62" s="11">
         <v>1</v>
       </c>
-      <c r="F62" s="14">
-        <v>0</v>
-      </c>
-      <c r="G62" s="14">
+      <c r="F62" s="11">
+        <v>18</v>
+      </c>
+      <c r="G62" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="7"/>
-      <c r="B63" s="12"/>
-      <c r="C63" s="13"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-    </row>
-    <row r="64" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B63" s="9"/>
+      <c r="C63" s="10"/>
+      <c r="D63" s="11"/>
+      <c r="E63" s="11"/>
+      <c r="F63" s="11"/>
+      <c r="G63" s="11"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B64" s="12"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
+        <v>27</v>
+      </c>
+      <c r="B64" s="9"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="11"/>
+      <c r="E64" s="11"/>
+      <c r="F64" s="11"/>
+      <c r="G64" s="11"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="6">
         <v>22</v>
       </c>
-      <c r="B65" s="12" t="s">
+      <c r="B65" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C65" s="13">
-        <v>31.4</v>
-      </c>
-      <c r="D65" s="14">
-        <v>31.4</v>
-      </c>
-      <c r="E65" s="14">
+      <c r="C65" s="10">
+        <v>35.9</v>
+      </c>
+      <c r="D65" s="11">
+        <v>35.9</v>
+      </c>
+      <c r="E65" s="11">
         <v>1</v>
       </c>
-      <c r="F65" s="14">
-        <v>31</v>
-      </c>
-      <c r="G65" s="14" t="s">
-        <v>11</v>
+      <c r="F65" s="11">
+        <v>0</v>
+      </c>
+      <c r="G65" s="11">
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="7"/>
-      <c r="B66" s="12"/>
-      <c r="C66" s="13"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-    </row>
-    <row r="67" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B66" s="9"/>
+      <c r="C66" s="10"/>
+      <c r="D66" s="11"/>
+      <c r="E66" s="11"/>
+      <c r="F66" s="11"/>
+      <c r="G66" s="11"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B67" s="12"/>
-      <c r="C67" s="13"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
+        <v>28</v>
+      </c>
+      <c r="B67" s="9"/>
+      <c r="C67" s="10"/>
+      <c r="D67" s="11"/>
+      <c r="E67" s="11"/>
+      <c r="F67" s="11"/>
+      <c r="G67" s="11"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="6">
         <v>23</v>
       </c>
-      <c r="B68" s="12" t="s">
+      <c r="B68" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C68" s="13">
-        <v>25</v>
-      </c>
-      <c r="D68" s="14">
-        <v>25</v>
-      </c>
-      <c r="E68" s="14">
+      <c r="C68" s="10">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="D68" s="11">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="E68" s="11">
         <v>1</v>
       </c>
-      <c r="F68" s="14">
-        <v>3</v>
-      </c>
-      <c r="G68" s="14">
-        <v>1</v>
+      <c r="F68" s="11">
+        <v>6</v>
+      </c>
+      <c r="G68" s="11">
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="7"/>
-      <c r="B69" s="12"/>
-      <c r="C69" s="13"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
-    </row>
-    <row r="70" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B69" s="9"/>
+      <c r="C69" s="10"/>
+      <c r="D69" s="11"/>
+      <c r="E69" s="11"/>
+      <c r="F69" s="11"/>
+      <c r="G69" s="11"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B70" s="12"/>
-      <c r="C70" s="13"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
+        <v>29</v>
+      </c>
+      <c r="B70" s="9"/>
+      <c r="C70" s="10"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="11"/>
+      <c r="F70" s="11"/>
+      <c r="G70" s="11"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="6">
         <v>24</v>
       </c>
-      <c r="B71" s="12" t="s">
+      <c r="B71" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C71" s="13">
-        <v>24.1</v>
-      </c>
-      <c r="D71" s="14">
-        <v>24.1</v>
-      </c>
-      <c r="E71" s="14">
+      <c r="C71" s="10">
+        <v>31.9</v>
+      </c>
+      <c r="D71" s="11">
+        <v>31.9</v>
+      </c>
+      <c r="E71" s="11">
         <v>1</v>
       </c>
-      <c r="F71" s="14">
+      <c r="F71" s="11">
         <v>0</v>
       </c>
-      <c r="G71" s="14" t="s">
+      <c r="G71" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="7"/>
-      <c r="B72" s="12"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
-    </row>
-    <row r="73" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B72" s="9"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="11"/>
+      <c r="G72" s="11"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B73" s="12"/>
-      <c r="C73" s="13"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
+        <v>30</v>
+      </c>
+      <c r="B73" s="9"/>
+      <c r="C73" s="10"/>
+      <c r="D73" s="11"/>
+      <c r="E73" s="11"/>
+      <c r="F73" s="11"/>
+      <c r="G73" s="11"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="6">
         <v>25</v>
       </c>
-      <c r="B74" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C74" s="13">
-        <v>18.3</v>
-      </c>
-      <c r="D74" s="14">
-        <v>18.3</v>
-      </c>
-      <c r="E74" s="14">
+      <c r="B74" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C74" s="10">
+        <v>31.7</v>
+      </c>
+      <c r="D74" s="11">
+        <v>31.7</v>
+      </c>
+      <c r="E74" s="11">
         <v>1</v>
       </c>
-      <c r="F74" s="14">
+      <c r="F74" s="11">
         <v>0</v>
       </c>
-      <c r="G74" s="14">
+      <c r="G74" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="7"/>
-      <c r="B75" s="12"/>
-      <c r="C75" s="13"/>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="14"/>
-    </row>
-    <row r="76" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B75" s="9"/>
+      <c r="C75" s="10"/>
+      <c r="D75" s="11"/>
+      <c r="E75" s="11"/>
+      <c r="F75" s="11"/>
+      <c r="G75" s="11"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B76" s="12"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
-      <c r="G76" s="14"/>
+        <v>31</v>
+      </c>
+      <c r="B76" s="9"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="11"/>
+      <c r="E76" s="11"/>
+      <c r="F76" s="11"/>
+      <c r="G76" s="11"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="6">
         <v>26</v>
       </c>
-      <c r="B77" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C77" s="13">
-        <v>18.100000000000001</v>
-      </c>
-      <c r="D77" s="14">
-        <v>18.100000000000001</v>
-      </c>
-      <c r="E77" s="14">
+      <c r="B77" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C77" s="10">
+        <v>31.4</v>
+      </c>
+      <c r="D77" s="11">
+        <v>31.4</v>
+      </c>
+      <c r="E77" s="11">
         <v>1</v>
       </c>
-      <c r="F77" s="14">
-        <v>16</v>
-      </c>
-      <c r="G77" s="14" t="s">
-        <v>11</v>
+      <c r="F77" s="11">
+        <v>0</v>
+      </c>
+      <c r="G77" s="11">
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="7"/>
-      <c r="B78" s="12"/>
-      <c r="C78" s="13"/>
-      <c r="D78" s="14"/>
-      <c r="E78" s="14"/>
-      <c r="F78" s="14"/>
-      <c r="G78" s="14"/>
-    </row>
-    <row r="79" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B78" s="9"/>
+      <c r="C78" s="10"/>
+      <c r="D78" s="11"/>
+      <c r="E78" s="11"/>
+      <c r="F78" s="11"/>
+      <c r="G78" s="11"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B79" s="12"/>
-      <c r="C79" s="13"/>
-      <c r="D79" s="14"/>
-      <c r="E79" s="14"/>
-      <c r="F79" s="14"/>
-      <c r="G79" s="14"/>
+        <v>32</v>
+      </c>
+      <c r="B79" s="9"/>
+      <c r="C79" s="10"/>
+      <c r="D79" s="11"/>
+      <c r="E79" s="11"/>
+      <c r="F79" s="11"/>
+      <c r="G79" s="11"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="6">
         <v>27</v>
       </c>
-      <c r="B80" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C80" s="13">
-        <v>17</v>
-      </c>
-      <c r="D80" s="14">
-        <v>17</v>
-      </c>
-      <c r="E80" s="14">
+      <c r="B80" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C80" s="10">
+        <v>31.4</v>
+      </c>
+      <c r="D80" s="11">
+        <v>31.4</v>
+      </c>
+      <c r="E80" s="11">
         <v>1</v>
       </c>
-      <c r="F80" s="14">
+      <c r="F80" s="11">
         <v>31</v>
       </c>
-      <c r="G80" s="14" t="s">
+      <c r="G80" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="7"/>
-      <c r="B81" s="12"/>
-      <c r="C81" s="13"/>
-      <c r="D81" s="14"/>
-      <c r="E81" s="14"/>
-      <c r="F81" s="14"/>
-      <c r="G81" s="14"/>
-    </row>
-    <row r="82" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B81" s="9"/>
+      <c r="C81" s="10"/>
+      <c r="D81" s="11"/>
+      <c r="E81" s="11"/>
+      <c r="F81" s="11"/>
+      <c r="G81" s="11"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B82" s="12"/>
-      <c r="C82" s="13"/>
-      <c r="D82" s="14"/>
-      <c r="E82" s="14"/>
-      <c r="F82" s="14"/>
-      <c r="G82" s="14"/>
+        <v>33</v>
+      </c>
+      <c r="B82" s="9"/>
+      <c r="C82" s="10"/>
+      <c r="D82" s="11"/>
+      <c r="E82" s="11"/>
+      <c r="F82" s="11"/>
+      <c r="G82" s="11"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="6">
         <v>28</v>
       </c>
-      <c r="B83" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C83" s="13">
-        <v>16</v>
-      </c>
-      <c r="D83" s="14">
-        <v>16</v>
-      </c>
-      <c r="E83" s="14">
+      <c r="B83" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C83" s="10">
+        <v>27.1</v>
+      </c>
+      <c r="D83" s="11">
+        <v>27.1</v>
+      </c>
+      <c r="E83" s="11">
         <v>1</v>
       </c>
-      <c r="F83" s="14">
-        <v>20</v>
-      </c>
-      <c r="G83" s="14" t="s">
+      <c r="F83" s="11">
+        <v>18</v>
+      </c>
+      <c r="G83" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="7"/>
-      <c r="B84" s="12"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="14"/>
-      <c r="E84" s="14"/>
-      <c r="F84" s="14"/>
-      <c r="G84" s="14"/>
-    </row>
-    <row r="85" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B84" s="9"/>
+      <c r="C84" s="10"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="11"/>
+      <c r="F84" s="11"/>
+      <c r="G84" s="11"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B85" s="12"/>
-      <c r="C85" s="13"/>
-      <c r="D85" s="14"/>
-      <c r="E85" s="14"/>
-      <c r="F85" s="14"/>
-      <c r="G85" s="14"/>
+        <v>67</v>
+      </c>
+      <c r="B85" s="9"/>
+      <c r="C85" s="10"/>
+      <c r="D85" s="11"/>
+      <c r="E85" s="11"/>
+      <c r="F85" s="11"/>
+      <c r="G85" s="11"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="6">
         <v>29</v>
       </c>
-      <c r="B86" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C86" s="13">
-        <v>15.1</v>
-      </c>
-      <c r="D86" s="14">
-        <v>15.1</v>
-      </c>
-      <c r="E86" s="14">
+      <c r="B86" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C86" s="10">
+        <v>25.3</v>
+      </c>
+      <c r="D86" s="11">
+        <v>25.3</v>
+      </c>
+      <c r="E86" s="11">
         <v>1</v>
       </c>
-      <c r="F86" s="14">
-        <v>18</v>
-      </c>
-      <c r="G86" s="14" t="s">
-        <v>11</v>
+      <c r="F86" s="11">
+        <v>0</v>
+      </c>
+      <c r="G86" s="11">
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="7"/>
-      <c r="B87" s="12"/>
-      <c r="C87" s="13"/>
-      <c r="D87" s="14"/>
-      <c r="E87" s="14"/>
-      <c r="F87" s="14"/>
-      <c r="G87" s="14"/>
-    </row>
-    <row r="88" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B87" s="9"/>
+      <c r="C87" s="10"/>
+      <c r="D87" s="11"/>
+      <c r="E87" s="11"/>
+      <c r="F87" s="11"/>
+      <c r="G87" s="11"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B88" s="12"/>
-      <c r="C88" s="13"/>
-      <c r="D88" s="14"/>
-      <c r="E88" s="14"/>
-      <c r="F88" s="14"/>
-      <c r="G88" s="14"/>
+        <v>68</v>
+      </c>
+      <c r="B88" s="9"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="11"/>
+      <c r="E88" s="11"/>
+      <c r="F88" s="11"/>
+      <c r="G88" s="11"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="6">
         <v>30</v>
       </c>
-      <c r="B89" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C89" s="13">
-        <v>10.1</v>
-      </c>
-      <c r="D89" s="14">
-        <v>10.1</v>
-      </c>
-      <c r="E89" s="14">
+      <c r="B89" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C89" s="10">
+        <v>25</v>
+      </c>
+      <c r="D89" s="11">
+        <v>25</v>
+      </c>
+      <c r="E89" s="11">
         <v>1</v>
       </c>
-      <c r="F89" s="14">
-        <v>16</v>
-      </c>
-      <c r="G89" s="14" t="s">
-        <v>11</v>
+      <c r="F89" s="11">
+        <v>3</v>
+      </c>
+      <c r="G89" s="11">
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="7"/>
-      <c r="B90" s="12"/>
-      <c r="C90" s="13"/>
-      <c r="D90" s="14"/>
-      <c r="E90" s="14"/>
-      <c r="F90" s="14"/>
-      <c r="G90" s="14"/>
-    </row>
-    <row r="91" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B90" s="9"/>
+      <c r="C90" s="10"/>
+      <c r="D90" s="11"/>
+      <c r="E90" s="11"/>
+      <c r="F90" s="11"/>
+      <c r="G90" s="11"/>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B91" s="12"/>
-      <c r="C91" s="13"/>
-      <c r="D91" s="14"/>
-      <c r="E91" s="14"/>
-      <c r="F91" s="14"/>
-      <c r="G91" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="B91" s="9"/>
+      <c r="C91" s="10"/>
+      <c r="D91" s="11"/>
+      <c r="E91" s="11"/>
+      <c r="F91" s="11"/>
+      <c r="G91" s="11"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="6">
         <v>31</v>
       </c>
-      <c r="B92" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C92" s="13">
-        <v>8.5</v>
-      </c>
-      <c r="D92" s="14">
-        <v>8.5</v>
-      </c>
-      <c r="E92" s="14">
+      <c r="B92" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C92" s="10">
+        <v>24.7</v>
+      </c>
+      <c r="D92" s="11">
+        <v>24.7</v>
+      </c>
+      <c r="E92" s="11">
         <v>1</v>
       </c>
-      <c r="F92" s="14">
-        <v>0</v>
-      </c>
-      <c r="G92" s="14" t="s">
+      <c r="F92" s="11">
+        <v>38</v>
+      </c>
+      <c r="G92" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="7"/>
-      <c r="B93" s="12"/>
-      <c r="C93" s="13"/>
-      <c r="D93" s="14"/>
-      <c r="E93" s="14"/>
-      <c r="F93" s="14"/>
-      <c r="G93" s="14"/>
-    </row>
-    <row r="94" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B93" s="9"/>
+      <c r="C93" s="10"/>
+      <c r="D93" s="11"/>
+      <c r="E93" s="11"/>
+      <c r="F93" s="11"/>
+      <c r="G93" s="11"/>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B94" s="12"/>
-      <c r="C94" s="13"/>
-      <c r="D94" s="14"/>
-      <c r="E94" s="14"/>
-      <c r="F94" s="14"/>
-      <c r="G94" s="14"/>
+        <v>69</v>
+      </c>
+      <c r="B94" s="9"/>
+      <c r="C94" s="10"/>
+      <c r="D94" s="11"/>
+      <c r="E94" s="11"/>
+      <c r="F94" s="11"/>
+      <c r="G94" s="11"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="6">
         <v>32</v>
       </c>
-      <c r="B95" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C95" s="13">
-        <v>7.2</v>
-      </c>
-      <c r="D95" s="14">
-        <v>7.2</v>
-      </c>
-      <c r="E95" s="14">
+      <c r="B95" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C95" s="10">
+        <v>24.2</v>
+      </c>
+      <c r="D95" s="11">
+        <v>24.2</v>
+      </c>
+      <c r="E95" s="11">
         <v>1</v>
       </c>
-      <c r="F95" s="14">
-        <v>33</v>
-      </c>
-      <c r="G95" s="14" t="s">
+      <c r="F95" s="11">
+        <v>17</v>
+      </c>
+      <c r="G95" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="7"/>
-      <c r="B96" s="12"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="14"/>
-      <c r="E96" s="14"/>
-      <c r="F96" s="14"/>
-      <c r="G96" s="14"/>
-    </row>
-    <row r="97" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B96" s="9"/>
+      <c r="C96" s="10"/>
+      <c r="D96" s="11"/>
+      <c r="E96" s="11"/>
+      <c r="F96" s="11"/>
+      <c r="G96" s="11"/>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B97" s="12"/>
-      <c r="C97" s="13"/>
-      <c r="D97" s="14"/>
-      <c r="E97" s="14"/>
-      <c r="F97" s="14"/>
-      <c r="G97" s="14"/>
+        <v>70</v>
+      </c>
+      <c r="B97" s="9"/>
+      <c r="C97" s="10"/>
+      <c r="D97" s="11"/>
+      <c r="E97" s="11"/>
+      <c r="F97" s="11"/>
+      <c r="G97" s="11"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="6">
         <v>33</v>
       </c>
-      <c r="B98" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C98" s="13">
-        <v>6.4</v>
-      </c>
-      <c r="D98" s="14">
-        <v>6.4</v>
-      </c>
-      <c r="E98" s="14">
+      <c r="B98" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C98" s="10">
+        <v>24.1</v>
+      </c>
+      <c r="D98" s="11">
+        <v>24.1</v>
+      </c>
+      <c r="E98" s="11">
         <v>1</v>
       </c>
-      <c r="F98" s="14">
+      <c r="F98" s="11">
         <v>0</v>
       </c>
-      <c r="G98" s="14" t="s">
+      <c r="G98" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="7"/>
-      <c r="B99" s="12"/>
-      <c r="C99" s="13"/>
-      <c r="D99" s="14"/>
-      <c r="E99" s="14"/>
-      <c r="F99" s="14"/>
-      <c r="G99" s="14"/>
-    </row>
-    <row r="100" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B99" s="9"/>
+      <c r="C99" s="10"/>
+      <c r="D99" s="11"/>
+      <c r="E99" s="11"/>
+      <c r="F99" s="11"/>
+      <c r="G99" s="11"/>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B100" s="12"/>
-      <c r="C100" s="13"/>
-      <c r="D100" s="14"/>
-      <c r="E100" s="14"/>
-      <c r="F100" s="14"/>
-      <c r="G100" s="14"/>
+        <v>35</v>
+      </c>
+      <c r="B100" s="9"/>
+      <c r="C100" s="10"/>
+      <c r="D100" s="11"/>
+      <c r="E100" s="11"/>
+      <c r="F100" s="11"/>
+      <c r="G100" s="11"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="6">
         <v>34</v>
       </c>
-      <c r="B101" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C101" s="13">
-        <v>4.8</v>
-      </c>
-      <c r="D101" s="14">
-        <v>4.8</v>
-      </c>
-      <c r="E101" s="14">
+      <c r="B101" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C101" s="10">
+        <v>22.2</v>
+      </c>
+      <c r="D101" s="11">
+        <v>22.2</v>
+      </c>
+      <c r="E101" s="11">
         <v>1</v>
       </c>
-      <c r="F101" s="14">
-        <v>9</v>
-      </c>
-      <c r="G101" s="14" t="s">
-        <v>11</v>
+      <c r="F101" s="11">
+        <v>7</v>
+      </c>
+      <c r="G101" s="11">
+        <v>2</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="7"/>
-      <c r="B102" s="12"/>
-      <c r="C102" s="13"/>
-      <c r="D102" s="14"/>
-      <c r="E102" s="14"/>
-      <c r="F102" s="14"/>
-      <c r="G102" s="14"/>
-    </row>
-    <row r="103" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B102" s="9"/>
+      <c r="C102" s="10"/>
+      <c r="D102" s="11"/>
+      <c r="E102" s="11"/>
+      <c r="F102" s="11"/>
+      <c r="G102" s="11"/>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B103" s="12"/>
-      <c r="C103" s="13"/>
-      <c r="D103" s="14"/>
-      <c r="E103" s="14"/>
-      <c r="F103" s="14"/>
-      <c r="G103" s="14"/>
+        <v>71</v>
+      </c>
+      <c r="B103" s="9"/>
+      <c r="C103" s="10"/>
+      <c r="D103" s="11"/>
+      <c r="E103" s="11"/>
+      <c r="F103" s="11"/>
+      <c r="G103" s="11"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="6">
         <v>35</v>
       </c>
-      <c r="B104" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C104" s="13">
-        <v>4.5</v>
-      </c>
-      <c r="D104" s="14">
-        <v>4.5</v>
-      </c>
-      <c r="E104" s="14">
+      <c r="B104" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C104" s="10">
+        <v>21.2</v>
+      </c>
+      <c r="D104" s="11">
+        <v>21.2</v>
+      </c>
+      <c r="E104" s="11">
         <v>1</v>
       </c>
-      <c r="F104" s="14">
-        <v>5</v>
-      </c>
-      <c r="G104" s="14" t="s">
-        <v>11</v>
+      <c r="F104" s="11">
+        <v>0</v>
+      </c>
+      <c r="G104" s="11">
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="7"/>
-      <c r="B105" s="12"/>
-      <c r="C105" s="13"/>
-      <c r="D105" s="14"/>
-      <c r="E105" s="14"/>
-      <c r="F105" s="14"/>
-      <c r="G105" s="14"/>
-    </row>
-    <row r="106" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B105" s="9"/>
+      <c r="C105" s="10"/>
+      <c r="D105" s="11"/>
+      <c r="E105" s="11"/>
+      <c r="F105" s="11"/>
+      <c r="G105" s="11"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B106" s="12"/>
-      <c r="C106" s="13"/>
-      <c r="D106" s="14"/>
-      <c r="E106" s="14"/>
-      <c r="F106" s="14"/>
-      <c r="G106" s="14"/>
+        <v>72</v>
+      </c>
+      <c r="B106" s="9"/>
+      <c r="C106" s="10"/>
+      <c r="D106" s="11"/>
+      <c r="E106" s="11"/>
+      <c r="F106" s="11"/>
+      <c r="G106" s="11"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="6">
         <v>36</v>
       </c>
-      <c r="B107" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C107" s="13">
-        <v>4</v>
-      </c>
-      <c r="D107" s="14">
-        <v>4</v>
-      </c>
-      <c r="E107" s="14">
+      <c r="B107" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C107" s="10">
+        <v>18.3</v>
+      </c>
+      <c r="D107" s="11">
+        <v>18.3</v>
+      </c>
+      <c r="E107" s="11">
         <v>1</v>
       </c>
-      <c r="F107" s="14">
-        <v>11</v>
-      </c>
-      <c r="G107" s="14" t="s">
-        <v>11</v>
+      <c r="F107" s="11">
+        <v>0</v>
+      </c>
+      <c r="G107" s="11">
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="7"/>
-      <c r="B108" s="12"/>
-      <c r="C108" s="13"/>
-      <c r="D108" s="14"/>
-      <c r="E108" s="14"/>
-      <c r="F108" s="14"/>
-      <c r="G108" s="14"/>
-    </row>
-    <row r="109" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B108" s="9"/>
+      <c r="C108" s="10"/>
+      <c r="D108" s="11"/>
+      <c r="E108" s="11"/>
+      <c r="F108" s="11"/>
+      <c r="G108" s="11"/>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B109" s="12"/>
-      <c r="C109" s="13"/>
-      <c r="D109" s="14"/>
-      <c r="E109" s="14"/>
-      <c r="F109" s="14"/>
-      <c r="G109" s="14"/>
+        <v>36</v>
+      </c>
+      <c r="B109" s="9"/>
+      <c r="C109" s="10"/>
+      <c r="D109" s="11"/>
+      <c r="E109" s="11"/>
+      <c r="F109" s="11"/>
+      <c r="G109" s="11"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="6">
         <v>37</v>
       </c>
-      <c r="B110" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C110" s="13">
-        <v>3</v>
-      </c>
-      <c r="D110" s="14">
-        <v>3</v>
-      </c>
-      <c r="E110" s="14">
+      <c r="B110" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C110" s="10">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="D110" s="11">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E110" s="11">
         <v>1</v>
       </c>
-      <c r="F110" s="14">
-        <v>0</v>
-      </c>
-      <c r="G110" s="14" t="s">
+      <c r="F110" s="11">
+        <v>16</v>
+      </c>
+      <c r="G110" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="7"/>
-      <c r="B111" s="12"/>
-      <c r="C111" s="13"/>
-      <c r="D111" s="14"/>
-      <c r="E111" s="14"/>
-      <c r="F111" s="14"/>
-      <c r="G111" s="14"/>
-    </row>
-    <row r="112" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B111" s="9"/>
+      <c r="C111" s="10"/>
+      <c r="D111" s="11"/>
+      <c r="E111" s="11"/>
+      <c r="F111" s="11"/>
+      <c r="G111" s="11"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B112" s="12"/>
-      <c r="C112" s="13"/>
-      <c r="D112" s="14"/>
-      <c r="E112" s="14"/>
-      <c r="F112" s="14"/>
-      <c r="G112" s="14"/>
+        <v>37</v>
+      </c>
+      <c r="B112" s="9"/>
+      <c r="C112" s="10"/>
+      <c r="D112" s="11"/>
+      <c r="E112" s="11"/>
+      <c r="F112" s="11"/>
+      <c r="G112" s="11"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="6">
         <v>38</v>
       </c>
-      <c r="B113" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C113" s="13">
-        <v>2</v>
-      </c>
-      <c r="D113" s="14">
-        <v>2</v>
-      </c>
-      <c r="E113" s="14">
+      <c r="B113" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C113" s="10">
+        <v>17</v>
+      </c>
+      <c r="D113" s="11">
+        <v>17</v>
+      </c>
+      <c r="E113" s="11">
         <v>1</v>
       </c>
-      <c r="F113" s="14">
-        <v>0</v>
-      </c>
-      <c r="G113" s="14" t="s">
+      <c r="F113" s="11">
+        <v>31</v>
+      </c>
+      <c r="G113" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="7"/>
-      <c r="B114" s="12"/>
-      <c r="C114" s="13"/>
-      <c r="D114" s="14"/>
-      <c r="E114" s="14"/>
-      <c r="F114" s="14"/>
-      <c r="G114" s="14"/>
-    </row>
-    <row r="115" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B114" s="9"/>
+      <c r="C114" s="10"/>
+      <c r="D114" s="11"/>
+      <c r="E114" s="11"/>
+      <c r="F114" s="11"/>
+      <c r="G114" s="11"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B115" s="12"/>
-      <c r="C115" s="13"/>
-      <c r="D115" s="14"/>
-      <c r="E115" s="14"/>
-      <c r="F115" s="14"/>
-      <c r="G115" s="14"/>
+        <v>38</v>
+      </c>
+      <c r="B115" s="9"/>
+      <c r="C115" s="10"/>
+      <c r="D115" s="11"/>
+      <c r="E115" s="11"/>
+      <c r="F115" s="11"/>
+      <c r="G115" s="11"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="6">
         <v>39</v>
       </c>
-      <c r="B116" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C116" s="13">
-        <v>1.5</v>
-      </c>
-      <c r="D116" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="E116" s="14">
+      <c r="B116" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C116" s="10">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="D116" s="11">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="E116" s="11">
         <v>1</v>
       </c>
-      <c r="F116" s="14">
-        <v>8</v>
-      </c>
-      <c r="G116" s="14" t="s">
+      <c r="F116" s="11">
+        <v>18</v>
+      </c>
+      <c r="G116" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="7"/>
-      <c r="B117" s="12"/>
-      <c r="C117" s="13"/>
-      <c r="D117" s="14"/>
-      <c r="E117" s="14"/>
-      <c r="F117" s="14"/>
-      <c r="G117" s="14"/>
+      <c r="B117" s="9"/>
+      <c r="C117" s="10"/>
+      <c r="D117" s="11"/>
+      <c r="E117" s="11"/>
+      <c r="F117" s="11"/>
+      <c r="G117" s="11"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="B118" s="12"/>
-      <c r="C118" s="13"/>
-      <c r="D118" s="14"/>
-      <c r="E118" s="14"/>
-      <c r="F118" s="14"/>
-      <c r="G118" s="14"/>
+        <v>73</v>
+      </c>
+      <c r="B118" s="9"/>
+      <c r="C118" s="10"/>
+      <c r="D118" s="11"/>
+      <c r="E118" s="11"/>
+      <c r="F118" s="11"/>
+      <c r="G118" s="11"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="6">
         <v>40</v>
       </c>
-      <c r="B119" s="12" t="s">
+      <c r="B119" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C119" s="13">
-        <v>0</v>
-      </c>
-      <c r="D119" s="14">
-        <v>0</v>
-      </c>
-      <c r="E119" s="14">
+      <c r="C119" s="10">
+        <v>16</v>
+      </c>
+      <c r="D119" s="11">
+        <v>16</v>
+      </c>
+      <c r="E119" s="11">
         <v>1</v>
       </c>
-      <c r="F119" s="14">
-        <v>0</v>
-      </c>
-      <c r="G119" s="14" t="s">
+      <c r="F119" s="11">
+        <v>20</v>
+      </c>
+      <c r="G119" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" s="7"/>
-      <c r="B120" s="12"/>
-      <c r="C120" s="13"/>
-      <c r="D120" s="14"/>
-      <c r="E120" s="14"/>
-      <c r="F120" s="14"/>
-      <c r="G120" s="14"/>
-    </row>
-    <row r="121" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B120" s="9"/>
+      <c r="C120" s="10"/>
+      <c r="D120" s="11"/>
+      <c r="E120" s="11"/>
+      <c r="F120" s="11"/>
+      <c r="G120" s="11"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B121" s="12"/>
-      <c r="C121" s="13"/>
-      <c r="D121" s="14"/>
-      <c r="E121" s="14"/>
-      <c r="F121" s="14"/>
-      <c r="G121" s="14"/>
+        <v>39</v>
+      </c>
+      <c r="B121" s="9"/>
+      <c r="C121" s="10"/>
+      <c r="D121" s="11"/>
+      <c r="E121" s="11"/>
+      <c r="F121" s="11"/>
+      <c r="G121" s="11"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="6">
         <v>41</v>
       </c>
-      <c r="B122" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C122" s="13">
-        <v>-0.6</v>
-      </c>
-      <c r="D122" s="14">
-        <v>-0.6</v>
-      </c>
-      <c r="E122" s="14">
+      <c r="B122" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C122" s="10">
+        <v>15.1</v>
+      </c>
+      <c r="D122" s="11">
+        <v>15.1</v>
+      </c>
+      <c r="E122" s="11">
         <v>1</v>
       </c>
-      <c r="F122" s="14">
-        <v>0</v>
-      </c>
-      <c r="G122" s="14" t="s">
+      <c r="F122" s="11">
+        <v>18</v>
+      </c>
+      <c r="G122" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" s="7"/>
-      <c r="B123" s="12"/>
-      <c r="C123" s="13"/>
-      <c r="D123" s="14"/>
-      <c r="E123" s="14"/>
-      <c r="F123" s="14"/>
-      <c r="G123" s="14"/>
-    </row>
-    <row r="124" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B123" s="9"/>
+      <c r="C123" s="10"/>
+      <c r="D123" s="11"/>
+      <c r="E123" s="11"/>
+      <c r="F123" s="11"/>
+      <c r="G123" s="11"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="B124" s="12"/>
-      <c r="C124" s="13"/>
-      <c r="D124" s="14"/>
-      <c r="E124" s="14"/>
-      <c r="F124" s="14"/>
-      <c r="G124" s="14"/>
+        <v>40</v>
+      </c>
+      <c r="B124" s="9"/>
+      <c r="C124" s="10"/>
+      <c r="D124" s="11"/>
+      <c r="E124" s="11"/>
+      <c r="F124" s="11"/>
+      <c r="G124" s="11"/>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" s="6">
         <v>42</v>
       </c>
-      <c r="B125" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C125" s="13">
-        <v>-1.3</v>
-      </c>
-      <c r="D125" s="14">
-        <v>-1.3</v>
-      </c>
-      <c r="E125" s="14">
+      <c r="B125" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C125" s="10">
+        <v>12.3</v>
+      </c>
+      <c r="D125" s="11">
+        <v>12.3</v>
+      </c>
+      <c r="E125" s="11">
         <v>1</v>
       </c>
-      <c r="F125" s="14">
+      <c r="F125" s="11">
         <v>0</v>
       </c>
-      <c r="G125" s="14" t="s">
-        <v>11</v>
+      <c r="G125" s="11">
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="7"/>
-      <c r="B126" s="12"/>
-      <c r="C126" s="13"/>
-      <c r="D126" s="14"/>
-      <c r="E126" s="14"/>
-      <c r="F126" s="14"/>
-      <c r="G126" s="14"/>
-    </row>
-    <row r="127" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B126" s="9"/>
+      <c r="C126" s="10"/>
+      <c r="D126" s="11"/>
+      <c r="E126" s="11"/>
+      <c r="F126" s="11"/>
+      <c r="G126" s="11"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B127" s="12"/>
-      <c r="C127" s="13"/>
-      <c r="D127" s="14"/>
-      <c r="E127" s="14"/>
-      <c r="F127" s="14"/>
-      <c r="G127" s="14"/>
+        <v>74</v>
+      </c>
+      <c r="B127" s="9"/>
+      <c r="C127" s="10"/>
+      <c r="D127" s="11"/>
+      <c r="E127" s="11"/>
+      <c r="F127" s="11"/>
+      <c r="G127" s="11"/>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" s="6">
         <v>43</v>
       </c>
-      <c r="B128" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C128" s="13">
-        <v>-3.7</v>
-      </c>
-      <c r="D128" s="14">
-        <v>-3.7</v>
-      </c>
-      <c r="E128" s="14">
+      <c r="B128" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C128" s="10">
+        <v>12.2</v>
+      </c>
+      <c r="D128" s="11">
+        <v>12.2</v>
+      </c>
+      <c r="E128" s="11">
         <v>1</v>
       </c>
-      <c r="F128" s="14">
-        <v>0</v>
-      </c>
-      <c r="G128" s="14" t="s">
+      <c r="F128" s="11">
+        <v>6</v>
+      </c>
+      <c r="G128" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" s="7"/>
-      <c r="B129" s="12"/>
-      <c r="C129" s="13"/>
-      <c r="D129" s="14"/>
-      <c r="E129" s="14"/>
-      <c r="F129" s="14"/>
-      <c r="G129" s="14"/>
-    </row>
-    <row r="130" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B129" s="9"/>
+      <c r="C129" s="10"/>
+      <c r="D129" s="11"/>
+      <c r="E129" s="11"/>
+      <c r="F129" s="11"/>
+      <c r="G129" s="11"/>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B130" s="12"/>
-      <c r="C130" s="13"/>
-      <c r="D130" s="14"/>
-      <c r="E130" s="14"/>
-      <c r="F130" s="14"/>
-      <c r="G130" s="14"/>
+        <v>75</v>
+      </c>
+      <c r="B130" s="9"/>
+      <c r="C130" s="10"/>
+      <c r="D130" s="11"/>
+      <c r="E130" s="11"/>
+      <c r="F130" s="11"/>
+      <c r="G130" s="11"/>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" s="6">
         <v>44</v>
       </c>
-      <c r="B131" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C131" s="13">
-        <v>-5.2</v>
-      </c>
-      <c r="D131" s="14">
-        <v>-5.2</v>
-      </c>
-      <c r="E131" s="14">
+      <c r="B131" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C131" s="10">
+        <v>10.1</v>
+      </c>
+      <c r="D131" s="11">
+        <v>10.1</v>
+      </c>
+      <c r="E131" s="11">
         <v>1</v>
       </c>
-      <c r="F131" s="14">
-        <v>0</v>
-      </c>
-      <c r="G131" s="14" t="s">
+      <c r="F131" s="11">
+        <v>16</v>
+      </c>
+      <c r="G131" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" s="7"/>
-      <c r="B132" s="12"/>
-      <c r="C132" s="13"/>
-      <c r="D132" s="14"/>
-      <c r="E132" s="14"/>
-      <c r="F132" s="14"/>
-      <c r="G132" s="14"/>
-    </row>
-    <row r="133" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B132" s="9"/>
+      <c r="C132" s="10"/>
+      <c r="D132" s="11"/>
+      <c r="E132" s="11"/>
+      <c r="F132" s="11"/>
+      <c r="G132" s="11"/>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B133" s="12"/>
-      <c r="C133" s="13"/>
-      <c r="D133" s="14"/>
-      <c r="E133" s="14"/>
-      <c r="F133" s="14"/>
-      <c r="G133" s="14"/>
+        <v>41</v>
+      </c>
+      <c r="B133" s="9"/>
+      <c r="C133" s="10"/>
+      <c r="D133" s="11"/>
+      <c r="E133" s="11"/>
+      <c r="F133" s="11"/>
+      <c r="G133" s="11"/>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="6">
         <v>45</v>
       </c>
-      <c r="B134" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C134" s="13">
-        <v>-6</v>
-      </c>
-      <c r="D134" s="14">
-        <v>-6</v>
-      </c>
-      <c r="E134" s="14">
+      <c r="B134" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C134" s="10">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="D134" s="11">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="E134" s="11">
         <v>1</v>
       </c>
-      <c r="F134" s="14">
-        <v>7</v>
-      </c>
-      <c r="G134" s="14" t="s">
+      <c r="F134" s="11">
+        <v>14</v>
+      </c>
+      <c r="G134" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" s="7"/>
-      <c r="B135" s="12"/>
-      <c r="C135" s="13"/>
-      <c r="D135" s="14"/>
-      <c r="E135" s="14"/>
-      <c r="F135" s="14"/>
-      <c r="G135" s="14"/>
-    </row>
-    <row r="136" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B135" s="9"/>
+      <c r="C135" s="10"/>
+      <c r="D135" s="11"/>
+      <c r="E135" s="11"/>
+      <c r="F135" s="11"/>
+      <c r="G135" s="11"/>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B136" s="12"/>
-      <c r="C136" s="13"/>
-      <c r="D136" s="14"/>
-      <c r="E136" s="14"/>
-      <c r="F136" s="14"/>
-      <c r="G136" s="14"/>
+        <v>76</v>
+      </c>
+      <c r="B136" s="9"/>
+      <c r="C136" s="10"/>
+      <c r="D136" s="11"/>
+      <c r="E136" s="11"/>
+      <c r="F136" s="11"/>
+      <c r="G136" s="11"/>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" s="6">
         <v>46</v>
       </c>
-      <c r="B137" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C137" s="13">
-        <v>-6.6</v>
-      </c>
-      <c r="D137" s="14">
-        <v>-6.6</v>
-      </c>
-      <c r="E137" s="14">
+      <c r="B137" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C137" s="10">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="D137" s="11">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="E137" s="11">
         <v>1</v>
       </c>
-      <c r="F137" s="14">
-        <v>4</v>
-      </c>
-      <c r="G137" s="14" t="s">
+      <c r="F137" s="11">
+        <v>0</v>
+      </c>
+      <c r="G137" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" s="7"/>
-      <c r="B138" s="12"/>
-      <c r="C138" s="13"/>
-      <c r="D138" s="14"/>
-      <c r="E138" s="14"/>
-      <c r="F138" s="14"/>
-      <c r="G138" s="14"/>
-    </row>
-    <row r="139" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B138" s="9"/>
+      <c r="C138" s="10"/>
+      <c r="D138" s="11"/>
+      <c r="E138" s="11"/>
+      <c r="F138" s="11"/>
+      <c r="G138" s="11"/>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B139" s="12"/>
-      <c r="C139" s="13"/>
-      <c r="D139" s="14"/>
-      <c r="E139" s="14"/>
-      <c r="F139" s="14"/>
-      <c r="G139" s="14"/>
+        <v>77</v>
+      </c>
+      <c r="B139" s="9"/>
+      <c r="C139" s="10"/>
+      <c r="D139" s="11"/>
+      <c r="E139" s="11"/>
+      <c r="F139" s="11"/>
+      <c r="G139" s="11"/>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="6">
         <v>47</v>
       </c>
-      <c r="B140" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C140" s="13">
-        <v>-7.5</v>
-      </c>
-      <c r="D140" s="14">
-        <v>-7.5</v>
-      </c>
-      <c r="E140" s="14">
+      <c r="B140" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C140" s="10">
+        <v>8.5</v>
+      </c>
+      <c r="D140" s="11">
+        <v>8.5</v>
+      </c>
+      <c r="E140" s="11">
         <v>1</v>
       </c>
-      <c r="F140" s="14">
-        <v>1</v>
-      </c>
-      <c r="G140" s="14" t="s">
+      <c r="F140" s="11">
+        <v>0</v>
+      </c>
+      <c r="G140" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" s="7"/>
-      <c r="B141" s="12"/>
-      <c r="C141" s="13"/>
-      <c r="D141" s="14"/>
-      <c r="E141" s="14"/>
-      <c r="F141" s="14"/>
-      <c r="G141" s="14"/>
-    </row>
-    <row r="142" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B141" s="9"/>
+      <c r="C141" s="10"/>
+      <c r="D141" s="11"/>
+      <c r="E141" s="11"/>
+      <c r="F141" s="11"/>
+      <c r="G141" s="11"/>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B142" s="12"/>
-      <c r="C142" s="13"/>
-      <c r="D142" s="14"/>
-      <c r="E142" s="14"/>
-      <c r="F142" s="14"/>
-      <c r="G142" s="14"/>
+        <v>42</v>
+      </c>
+      <c r="B142" s="9"/>
+      <c r="C142" s="10"/>
+      <c r="D142" s="11"/>
+      <c r="E142" s="11"/>
+      <c r="F142" s="11"/>
+      <c r="G142" s="11"/>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" s="6">
         <v>48</v>
       </c>
-      <c r="B143" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C143" s="13">
-        <v>-9.3000000000000007</v>
-      </c>
-      <c r="D143" s="14">
-        <v>-9.3000000000000007</v>
-      </c>
-      <c r="E143" s="14">
+      <c r="B143" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C143" s="10">
+        <v>7.2</v>
+      </c>
+      <c r="D143" s="11">
+        <v>7.2</v>
+      </c>
+      <c r="E143" s="11">
         <v>1</v>
       </c>
-      <c r="F143" s="14">
-        <v>0</v>
-      </c>
-      <c r="G143" s="14" t="s">
+      <c r="F143" s="11">
+        <v>33</v>
+      </c>
+      <c r="G143" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" s="7"/>
-      <c r="B144" s="12"/>
-      <c r="C144" s="13"/>
-      <c r="D144" s="14"/>
-      <c r="E144" s="14"/>
-      <c r="F144" s="14"/>
-      <c r="G144" s="14"/>
-    </row>
-    <row r="145" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B144" s="9"/>
+      <c r="C144" s="10"/>
+      <c r="D144" s="11"/>
+      <c r="E144" s="11"/>
+      <c r="F144" s="11"/>
+      <c r="G144" s="11"/>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B145" s="9"/>
+      <c r="C145" s="10"/>
+      <c r="D145" s="11"/>
+      <c r="E145" s="11"/>
+      <c r="F145" s="11"/>
+      <c r="G145" s="11"/>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A146" s="6">
+        <v>49</v>
+      </c>
+      <c r="B146" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C146" s="10">
+        <v>6.4</v>
+      </c>
+      <c r="D146" s="11">
+        <v>6.4</v>
+      </c>
+      <c r="E146" s="11">
+        <v>1</v>
+      </c>
+      <c r="F146" s="11">
+        <v>0</v>
+      </c>
+      <c r="G146" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A147" s="7"/>
+      <c r="B147" s="9"/>
+      <c r="C147" s="10"/>
+      <c r="D147" s="11"/>
+      <c r="E147" s="11"/>
+      <c r="F147" s="11"/>
+      <c r="G147" s="11"/>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A148" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B148" s="9"/>
+      <c r="C148" s="10"/>
+      <c r="D148" s="11"/>
+      <c r="E148" s="11"/>
+      <c r="F148" s="11"/>
+      <c r="G148" s="11"/>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A149" s="6">
+        <v>50</v>
+      </c>
+      <c r="B149" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C149" s="10">
+        <v>4.8</v>
+      </c>
+      <c r="D149" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="E149" s="11">
+        <v>1</v>
+      </c>
+      <c r="F149" s="11">
+        <v>9</v>
+      </c>
+      <c r="G149" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A150" s="7"/>
+      <c r="B150" s="9"/>
+      <c r="C150" s="10"/>
+      <c r="D150" s="11"/>
+      <c r="E150" s="11"/>
+      <c r="F150" s="11"/>
+      <c r="G150" s="11"/>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A151" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B151" s="9"/>
+      <c r="C151" s="10"/>
+      <c r="D151" s="11"/>
+      <c r="E151" s="11"/>
+      <c r="F151" s="11"/>
+      <c r="G151" s="11"/>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A152" s="6">
+        <v>51</v>
+      </c>
+      <c r="B152" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C152" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="D152" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="E152" s="11">
+        <v>1</v>
+      </c>
+      <c r="F152" s="11">
+        <v>5</v>
+      </c>
+      <c r="G152" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A153" s="7"/>
+      <c r="B153" s="9"/>
+      <c r="C153" s="10"/>
+      <c r="D153" s="11"/>
+      <c r="E153" s="11"/>
+      <c r="F153" s="11"/>
+      <c r="G153" s="11"/>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A154" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B154" s="9"/>
+      <c r="C154" s="10"/>
+      <c r="D154" s="11"/>
+      <c r="E154" s="11"/>
+      <c r="F154" s="11"/>
+      <c r="G154" s="11"/>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A155" s="6">
+        <v>52</v>
+      </c>
+      <c r="B155" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C155" s="10">
+        <v>4</v>
+      </c>
+      <c r="D155" s="11">
+        <v>4</v>
+      </c>
+      <c r="E155" s="11">
+        <v>1</v>
+      </c>
+      <c r="F155" s="11">
+        <v>11</v>
+      </c>
+      <c r="G155" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A156" s="7"/>
+      <c r="B156" s="9"/>
+      <c r="C156" s="10"/>
+      <c r="D156" s="11"/>
+      <c r="E156" s="11"/>
+      <c r="F156" s="11"/>
+      <c r="G156" s="11"/>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A157" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B157" s="9"/>
+      <c r="C157" s="10"/>
+      <c r="D157" s="11"/>
+      <c r="E157" s="11"/>
+      <c r="F157" s="11"/>
+      <c r="G157" s="11"/>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A158" s="6">
+        <v>53</v>
+      </c>
+      <c r="B158" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C158" s="10">
+        <v>3</v>
+      </c>
+      <c r="D158" s="11">
+        <v>3</v>
+      </c>
+      <c r="E158" s="11">
+        <v>1</v>
+      </c>
+      <c r="F158" s="11">
+        <v>0</v>
+      </c>
+      <c r="G158" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A159" s="7"/>
+      <c r="B159" s="9"/>
+      <c r="C159" s="10"/>
+      <c r="D159" s="11"/>
+      <c r="E159" s="11"/>
+      <c r="F159" s="11"/>
+      <c r="G159" s="11"/>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A160" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B160" s="9"/>
+      <c r="C160" s="10"/>
+      <c r="D160" s="11"/>
+      <c r="E160" s="11"/>
+      <c r="F160" s="11"/>
+      <c r="G160" s="11"/>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A161" s="6">
+        <v>54</v>
+      </c>
+      <c r="B161" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C161" s="10">
+        <v>2</v>
+      </c>
+      <c r="D161" s="11">
+        <v>2</v>
+      </c>
+      <c r="E161" s="11">
+        <v>1</v>
+      </c>
+      <c r="F161" s="11">
+        <v>6</v>
+      </c>
+      <c r="G161" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A162" s="7"/>
+      <c r="B162" s="9"/>
+      <c r="C162" s="10"/>
+      <c r="D162" s="11"/>
+      <c r="E162" s="11"/>
+      <c r="F162" s="11"/>
+      <c r="G162" s="11"/>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A163" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B163" s="9"/>
+      <c r="C163" s="10"/>
+      <c r="D163" s="11"/>
+      <c r="E163" s="11"/>
+      <c r="F163" s="11"/>
+      <c r="G163" s="11"/>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A164" s="6">
+        <v>55</v>
+      </c>
+      <c r="B164" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C164" s="10">
+        <v>2</v>
+      </c>
+      <c r="D164" s="11">
+        <v>2</v>
+      </c>
+      <c r="E164" s="11">
+        <v>1</v>
+      </c>
+      <c r="F164" s="11">
+        <v>0</v>
+      </c>
+      <c r="G164" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A165" s="7"/>
+      <c r="B165" s="9"/>
+      <c r="C165" s="10"/>
+      <c r="D165" s="11"/>
+      <c r="E165" s="11"/>
+      <c r="F165" s="11"/>
+      <c r="G165" s="11"/>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A166" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B166" s="9"/>
+      <c r="C166" s="10"/>
+      <c r="D166" s="11"/>
+      <c r="E166" s="11"/>
+      <c r="F166" s="11"/>
+      <c r="G166" s="11"/>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A167" s="6">
+        <v>56</v>
+      </c>
+      <c r="B167" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C167" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="D167" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="E167" s="11">
+        <v>1</v>
+      </c>
+      <c r="F167" s="11">
+        <v>8</v>
+      </c>
+      <c r="G167" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A168" s="7"/>
+      <c r="B168" s="9"/>
+      <c r="C168" s="10"/>
+      <c r="D168" s="11"/>
+      <c r="E168" s="11"/>
+      <c r="F168" s="11"/>
+      <c r="G168" s="11"/>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A169" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B169" s="9"/>
+      <c r="C169" s="10"/>
+      <c r="D169" s="11"/>
+      <c r="E169" s="11"/>
+      <c r="F169" s="11"/>
+      <c r="G169" s="11"/>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A170" s="6">
+        <v>57</v>
+      </c>
+      <c r="B170" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C170" s="10">
+        <v>0</v>
+      </c>
+      <c r="D170" s="11">
+        <v>0</v>
+      </c>
+      <c r="E170" s="11">
+        <v>1</v>
+      </c>
+      <c r="F170" s="11">
+        <v>0</v>
+      </c>
+      <c r="G170" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A171" s="7"/>
+      <c r="B171" s="9"/>
+      <c r="C171" s="10"/>
+      <c r="D171" s="11"/>
+      <c r="E171" s="11"/>
+      <c r="F171" s="11"/>
+      <c r="G171" s="11"/>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A172" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B172" s="9"/>
+      <c r="C172" s="10"/>
+      <c r="D172" s="11"/>
+      <c r="E172" s="11"/>
+      <c r="F172" s="11"/>
+      <c r="G172" s="11"/>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A173" s="6">
+        <v>58</v>
+      </c>
+      <c r="B173" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C173" s="10">
+        <v>0</v>
+      </c>
+      <c r="D173" s="11">
+        <v>0</v>
+      </c>
+      <c r="E173" s="11">
+        <v>1</v>
+      </c>
+      <c r="F173" s="11">
+        <v>0</v>
+      </c>
+      <c r="G173" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A174" s="7"/>
+      <c r="B174" s="9"/>
+      <c r="C174" s="10"/>
+      <c r="D174" s="11"/>
+      <c r="E174" s="11"/>
+      <c r="F174" s="11"/>
+      <c r="G174" s="11"/>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A175" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B175" s="9"/>
+      <c r="C175" s="10"/>
+      <c r="D175" s="11"/>
+      <c r="E175" s="11"/>
+      <c r="F175" s="11"/>
+      <c r="G175" s="11"/>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A176" s="6">
         <v>59</v>
       </c>
-      <c r="B145" s="12"/>
-      <c r="C145" s="13"/>
-      <c r="D145" s="14"/>
-      <c r="E145" s="14"/>
-      <c r="F145" s="14"/>
-      <c r="G145" s="14"/>
+      <c r="B176" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C176" s="10">
+        <v>-0.6</v>
+      </c>
+      <c r="D176" s="11">
+        <v>-0.6</v>
+      </c>
+      <c r="E176" s="11">
+        <v>1</v>
+      </c>
+      <c r="F176" s="11">
+        <v>0</v>
+      </c>
+      <c r="G176" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A177" s="7"/>
+      <c r="B177" s="9"/>
+      <c r="C177" s="10"/>
+      <c r="D177" s="11"/>
+      <c r="E177" s="11"/>
+      <c r="F177" s="11"/>
+      <c r="G177" s="11"/>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A178" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B178" s="9"/>
+      <c r="C178" s="10"/>
+      <c r="D178" s="11"/>
+      <c r="E178" s="11"/>
+      <c r="F178" s="11"/>
+      <c r="G178" s="11"/>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A179" s="6">
+        <v>60</v>
+      </c>
+      <c r="B179" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C179" s="10">
+        <v>-1.3</v>
+      </c>
+      <c r="D179" s="11">
+        <v>-1.3</v>
+      </c>
+      <c r="E179" s="11">
+        <v>1</v>
+      </c>
+      <c r="F179" s="11">
+        <v>0</v>
+      </c>
+      <c r="G179" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A180" s="7"/>
+      <c r="B180" s="9"/>
+      <c r="C180" s="10"/>
+      <c r="D180" s="11"/>
+      <c r="E180" s="11"/>
+      <c r="F180" s="11"/>
+      <c r="G180" s="11"/>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A181" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B181" s="9"/>
+      <c r="C181" s="10"/>
+      <c r="D181" s="11"/>
+      <c r="E181" s="11"/>
+      <c r="F181" s="11"/>
+      <c r="G181" s="11"/>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A182" s="6">
+        <v>61</v>
+      </c>
+      <c r="B182" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C182" s="10">
+        <v>-2</v>
+      </c>
+      <c r="D182" s="11">
+        <v>-2</v>
+      </c>
+      <c r="E182" s="11">
+        <v>1</v>
+      </c>
+      <c r="F182" s="11">
+        <v>0</v>
+      </c>
+      <c r="G182" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A183" s="7"/>
+      <c r="B183" s="9"/>
+      <c r="C183" s="10"/>
+      <c r="D183" s="11"/>
+      <c r="E183" s="11"/>
+      <c r="F183" s="11"/>
+      <c r="G183" s="11"/>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A184" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B184" s="9"/>
+      <c r="C184" s="10"/>
+      <c r="D184" s="11"/>
+      <c r="E184" s="11"/>
+      <c r="F184" s="11"/>
+      <c r="G184" s="11"/>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A185" s="6">
+        <v>62</v>
+      </c>
+      <c r="B185" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C185" s="10">
+        <v>-3.7</v>
+      </c>
+      <c r="D185" s="11">
+        <v>-3.7</v>
+      </c>
+      <c r="E185" s="11">
+        <v>1</v>
+      </c>
+      <c r="F185" s="11">
+        <v>0</v>
+      </c>
+      <c r="G185" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A186" s="7"/>
+      <c r="B186" s="9"/>
+      <c r="C186" s="10"/>
+      <c r="D186" s="11"/>
+      <c r="E186" s="11"/>
+      <c r="F186" s="11"/>
+      <c r="G186" s="11"/>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A187" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B187" s="9"/>
+      <c r="C187" s="10"/>
+      <c r="D187" s="11"/>
+      <c r="E187" s="11"/>
+      <c r="F187" s="11"/>
+      <c r="G187" s="11"/>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A188" s="6">
+        <v>63</v>
+      </c>
+      <c r="B188" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C188" s="10">
+        <v>-4.5999999999999996</v>
+      </c>
+      <c r="D188" s="11">
+        <v>-4.5999999999999996</v>
+      </c>
+      <c r="E188" s="11">
+        <v>1</v>
+      </c>
+      <c r="F188" s="11">
+        <v>6</v>
+      </c>
+      <c r="G188" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A189" s="7"/>
+      <c r="B189" s="9"/>
+      <c r="C189" s="10"/>
+      <c r="D189" s="11"/>
+      <c r="E189" s="11"/>
+      <c r="F189" s="11"/>
+      <c r="G189" s="11"/>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A190" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B190" s="9"/>
+      <c r="C190" s="10"/>
+      <c r="D190" s="11"/>
+      <c r="E190" s="11"/>
+      <c r="F190" s="11"/>
+      <c r="G190" s="11"/>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A191" s="6">
+        <v>64</v>
+      </c>
+      <c r="B191" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C191" s="10">
+        <v>-5.2</v>
+      </c>
+      <c r="D191" s="11">
+        <v>-5.2</v>
+      </c>
+      <c r="E191" s="11">
+        <v>1</v>
+      </c>
+      <c r="F191" s="11">
+        <v>0</v>
+      </c>
+      <c r="G191" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A192" s="7"/>
+      <c r="B192" s="9"/>
+      <c r="C192" s="10"/>
+      <c r="D192" s="11"/>
+      <c r="E192" s="11"/>
+      <c r="F192" s="11"/>
+      <c r="G192" s="11"/>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A193" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B193" s="9"/>
+      <c r="C193" s="10"/>
+      <c r="D193" s="11"/>
+      <c r="E193" s="11"/>
+      <c r="F193" s="11"/>
+      <c r="G193" s="11"/>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A194" s="6">
+        <v>65</v>
+      </c>
+      <c r="B194" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C194" s="10">
+        <v>-6</v>
+      </c>
+      <c r="D194" s="11">
+        <v>-6</v>
+      </c>
+      <c r="E194" s="11">
+        <v>1</v>
+      </c>
+      <c r="F194" s="11">
+        <v>7</v>
+      </c>
+      <c r="G194" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A195" s="7"/>
+      <c r="B195" s="9"/>
+      <c r="C195" s="10"/>
+      <c r="D195" s="11"/>
+      <c r="E195" s="11"/>
+      <c r="F195" s="11"/>
+      <c r="G195" s="11"/>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A196" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B196" s="9"/>
+      <c r="C196" s="10"/>
+      <c r="D196" s="11"/>
+      <c r="E196" s="11"/>
+      <c r="F196" s="11"/>
+      <c r="G196" s="11"/>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A197" s="6">
+        <v>66</v>
+      </c>
+      <c r="B197" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C197" s="10">
+        <v>-6.6</v>
+      </c>
+      <c r="D197" s="11">
+        <v>-6.6</v>
+      </c>
+      <c r="E197" s="11">
+        <v>1</v>
+      </c>
+      <c r="F197" s="11">
+        <v>4</v>
+      </c>
+      <c r="G197" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A198" s="7"/>
+      <c r="B198" s="9"/>
+      <c r="C198" s="10"/>
+      <c r="D198" s="11"/>
+      <c r="E198" s="11"/>
+      <c r="F198" s="11"/>
+      <c r="G198" s="11"/>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A199" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B199" s="9"/>
+      <c r="C199" s="10"/>
+      <c r="D199" s="11"/>
+      <c r="E199" s="11"/>
+      <c r="F199" s="11"/>
+      <c r="G199" s="11"/>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A200" s="6">
+        <v>67</v>
+      </c>
+      <c r="B200" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C200" s="10">
+        <v>-7.4</v>
+      </c>
+      <c r="D200" s="11">
+        <v>-7.4</v>
+      </c>
+      <c r="E200" s="11">
+        <v>1</v>
+      </c>
+      <c r="F200" s="11">
+        <v>2</v>
+      </c>
+      <c r="G200" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A201" s="7"/>
+      <c r="B201" s="9"/>
+      <c r="C201" s="10"/>
+      <c r="D201" s="11"/>
+      <c r="E201" s="11"/>
+      <c r="F201" s="11"/>
+      <c r="G201" s="11"/>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A202" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B202" s="9"/>
+      <c r="C202" s="10"/>
+      <c r="D202" s="11"/>
+      <c r="E202" s="11"/>
+      <c r="F202" s="11"/>
+      <c r="G202" s="11"/>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A203" s="6">
+        <v>68</v>
+      </c>
+      <c r="B203" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C203" s="10">
+        <v>-7.5</v>
+      </c>
+      <c r="D203" s="11">
+        <v>-7.5</v>
+      </c>
+      <c r="E203" s="11">
+        <v>1</v>
+      </c>
+      <c r="F203" s="11">
+        <v>1</v>
+      </c>
+      <c r="G203" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A204" s="7"/>
+      <c r="B204" s="9"/>
+      <c r="C204" s="10"/>
+      <c r="D204" s="11"/>
+      <c r="E204" s="11"/>
+      <c r="F204" s="11"/>
+      <c r="G204" s="11"/>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A205" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B205" s="9"/>
+      <c r="C205" s="10"/>
+      <c r="D205" s="11"/>
+      <c r="E205" s="11"/>
+      <c r="F205" s="11"/>
+      <c r="G205" s="11"/>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A206" s="6">
+        <v>69</v>
+      </c>
+      <c r="B206" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C206" s="10">
+        <v>-9.3000000000000007</v>
+      </c>
+      <c r="D206" s="11">
+        <v>-9.3000000000000007</v>
+      </c>
+      <c r="E206" s="11">
+        <v>1</v>
+      </c>
+      <c r="F206" s="11">
+        <v>0</v>
+      </c>
+      <c r="G206" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A207" s="7"/>
+      <c r="B207" s="9"/>
+      <c r="C207" s="10"/>
+      <c r="D207" s="11"/>
+      <c r="E207" s="11"/>
+      <c r="F207" s="11"/>
+      <c r="G207" s="11"/>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A208" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B208" s="9"/>
+      <c r="C208" s="10"/>
+      <c r="D208" s="11"/>
+      <c r="E208" s="11"/>
+      <c r="F208" s="11"/>
+      <c r="G208" s="11"/>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A209" s="6">
+        <v>70</v>
+      </c>
+      <c r="B209" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C209" s="10">
+        <v>-12.6</v>
+      </c>
+      <c r="D209" s="11">
+        <v>-12.6</v>
+      </c>
+      <c r="E209" s="11">
+        <v>1</v>
+      </c>
+      <c r="F209" s="11">
+        <v>1</v>
+      </c>
+      <c r="G209" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A210" s="7"/>
+      <c r="B210" s="9"/>
+      <c r="C210" s="10"/>
+      <c r="D210" s="11"/>
+      <c r="E210" s="11"/>
+      <c r="F210" s="11"/>
+      <c r="G210" s="11"/>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A211" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B211" s="9"/>
+      <c r="C211" s="10"/>
+      <c r="D211" s="11"/>
+      <c r="E211" s="11"/>
+      <c r="F211" s="11"/>
+      <c r="G211" s="11"/>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A212" s="6">
+        <v>71</v>
+      </c>
+      <c r="B212" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C212" s="10">
+        <v>-17.899999999999999</v>
+      </c>
+      <c r="D212" s="11">
+        <v>-17.899999999999999</v>
+      </c>
+      <c r="E212" s="11">
+        <v>1</v>
+      </c>
+      <c r="F212" s="11">
+        <v>5</v>
+      </c>
+      <c r="G212" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A213" s="7"/>
+      <c r="B213" s="9"/>
+      <c r="C213" s="10"/>
+      <c r="D213" s="11"/>
+      <c r="E213" s="11"/>
+      <c r="F213" s="11"/>
+      <c r="G213" s="11"/>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A214" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B214" s="9"/>
+      <c r="C214" s="10"/>
+      <c r="D214" s="11"/>
+      <c r="E214" s="11"/>
+      <c r="F214" s="11"/>
+      <c r="G214" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="288">
+  <mergeCells count="426">
+    <mergeCell ref="B212:B214"/>
+    <mergeCell ref="C212:C214"/>
+    <mergeCell ref="D212:D214"/>
+    <mergeCell ref="E212:E214"/>
+    <mergeCell ref="F212:F214"/>
+    <mergeCell ref="G212:G214"/>
+    <mergeCell ref="B206:B208"/>
+    <mergeCell ref="C206:C208"/>
+    <mergeCell ref="D206:D208"/>
+    <mergeCell ref="E206:E208"/>
+    <mergeCell ref="F206:F208"/>
+    <mergeCell ref="G206:G208"/>
+    <mergeCell ref="B209:B211"/>
+    <mergeCell ref="C209:C211"/>
+    <mergeCell ref="D209:D211"/>
+    <mergeCell ref="E209:E211"/>
+    <mergeCell ref="F209:F211"/>
+    <mergeCell ref="G209:G211"/>
+    <mergeCell ref="B200:B202"/>
+    <mergeCell ref="C200:C202"/>
+    <mergeCell ref="D200:D202"/>
+    <mergeCell ref="E200:E202"/>
+    <mergeCell ref="F200:F202"/>
+    <mergeCell ref="G200:G202"/>
+    <mergeCell ref="B203:B205"/>
+    <mergeCell ref="C203:C205"/>
+    <mergeCell ref="D203:D205"/>
+    <mergeCell ref="E203:E205"/>
+    <mergeCell ref="F203:F205"/>
+    <mergeCell ref="G203:G205"/>
+    <mergeCell ref="B194:B196"/>
+    <mergeCell ref="C194:C196"/>
+    <mergeCell ref="D194:D196"/>
+    <mergeCell ref="E194:E196"/>
+    <mergeCell ref="F194:F196"/>
+    <mergeCell ref="G194:G196"/>
+    <mergeCell ref="B197:B199"/>
+    <mergeCell ref="C197:C199"/>
+    <mergeCell ref="D197:D199"/>
+    <mergeCell ref="E197:E199"/>
+    <mergeCell ref="F197:F199"/>
+    <mergeCell ref="G197:G199"/>
+    <mergeCell ref="B188:B190"/>
+    <mergeCell ref="C188:C190"/>
+    <mergeCell ref="D188:D190"/>
+    <mergeCell ref="E188:E190"/>
+    <mergeCell ref="F188:F190"/>
+    <mergeCell ref="G188:G190"/>
+    <mergeCell ref="B191:B193"/>
+    <mergeCell ref="C191:C193"/>
+    <mergeCell ref="D191:D193"/>
+    <mergeCell ref="E191:E193"/>
+    <mergeCell ref="F191:F193"/>
+    <mergeCell ref="G191:G193"/>
+    <mergeCell ref="B182:B184"/>
+    <mergeCell ref="C182:C184"/>
+    <mergeCell ref="D182:D184"/>
+    <mergeCell ref="E182:E184"/>
+    <mergeCell ref="F182:F184"/>
+    <mergeCell ref="G182:G184"/>
+    <mergeCell ref="B185:B187"/>
+    <mergeCell ref="C185:C187"/>
+    <mergeCell ref="D185:D187"/>
+    <mergeCell ref="E185:E187"/>
+    <mergeCell ref="F185:F187"/>
+    <mergeCell ref="G185:G187"/>
+    <mergeCell ref="B176:B178"/>
+    <mergeCell ref="C176:C178"/>
+    <mergeCell ref="D176:D178"/>
+    <mergeCell ref="E176:E178"/>
+    <mergeCell ref="F176:F178"/>
+    <mergeCell ref="G176:G178"/>
+    <mergeCell ref="B179:B181"/>
+    <mergeCell ref="C179:C181"/>
+    <mergeCell ref="D179:D181"/>
+    <mergeCell ref="E179:E181"/>
+    <mergeCell ref="F179:F181"/>
+    <mergeCell ref="G179:G181"/>
+    <mergeCell ref="B170:B172"/>
+    <mergeCell ref="C170:C172"/>
+    <mergeCell ref="D170:D172"/>
+    <mergeCell ref="E170:E172"/>
+    <mergeCell ref="F170:F172"/>
+    <mergeCell ref="G170:G172"/>
+    <mergeCell ref="B173:B175"/>
+    <mergeCell ref="C173:C175"/>
+    <mergeCell ref="D173:D175"/>
+    <mergeCell ref="E173:E175"/>
+    <mergeCell ref="F173:F175"/>
+    <mergeCell ref="G173:G175"/>
+    <mergeCell ref="B164:B166"/>
+    <mergeCell ref="C164:C166"/>
+    <mergeCell ref="D164:D166"/>
+    <mergeCell ref="E164:E166"/>
+    <mergeCell ref="F164:F166"/>
+    <mergeCell ref="G164:G166"/>
+    <mergeCell ref="B167:B169"/>
+    <mergeCell ref="C167:C169"/>
+    <mergeCell ref="D167:D169"/>
+    <mergeCell ref="E167:E169"/>
+    <mergeCell ref="F167:F169"/>
+    <mergeCell ref="G167:G169"/>
+    <mergeCell ref="B158:B160"/>
+    <mergeCell ref="C158:C160"/>
+    <mergeCell ref="D158:D160"/>
+    <mergeCell ref="E158:E160"/>
+    <mergeCell ref="F158:F160"/>
+    <mergeCell ref="G158:G160"/>
+    <mergeCell ref="B161:B163"/>
+    <mergeCell ref="C161:C163"/>
+    <mergeCell ref="D161:D163"/>
+    <mergeCell ref="E161:E163"/>
+    <mergeCell ref="F161:F163"/>
+    <mergeCell ref="G161:G163"/>
+    <mergeCell ref="B152:B154"/>
+    <mergeCell ref="C152:C154"/>
+    <mergeCell ref="D152:D154"/>
+    <mergeCell ref="E152:E154"/>
+    <mergeCell ref="F152:F154"/>
+    <mergeCell ref="G152:G154"/>
+    <mergeCell ref="B155:B157"/>
+    <mergeCell ref="C155:C157"/>
+    <mergeCell ref="D155:D157"/>
+    <mergeCell ref="E155:E157"/>
+    <mergeCell ref="F155:F157"/>
+    <mergeCell ref="G155:G157"/>
+    <mergeCell ref="B146:B148"/>
+    <mergeCell ref="C146:C148"/>
+    <mergeCell ref="D146:D148"/>
+    <mergeCell ref="E146:E148"/>
+    <mergeCell ref="F146:F148"/>
+    <mergeCell ref="G146:G148"/>
+    <mergeCell ref="B149:B151"/>
+    <mergeCell ref="C149:C151"/>
+    <mergeCell ref="D149:D151"/>
+    <mergeCell ref="E149:E151"/>
+    <mergeCell ref="F149:F151"/>
+    <mergeCell ref="G149:G151"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="G2:G4"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="E11:E13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="G11:G13"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="G8:G10"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="E17:E19"/>
+    <mergeCell ref="F17:F19"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="D23:D25"/>
+    <mergeCell ref="E23:E25"/>
+    <mergeCell ref="F23:F25"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="F20:F22"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="E29:E31"/>
+    <mergeCell ref="F29:F31"/>
+    <mergeCell ref="G29:G31"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="D26:D28"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:C37"/>
+    <mergeCell ref="D35:D37"/>
+    <mergeCell ref="E35:E37"/>
+    <mergeCell ref="F35:F37"/>
+    <mergeCell ref="G35:G37"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="E32:E34"/>
+    <mergeCell ref="F32:F34"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="B41:B43"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="D41:D43"/>
+    <mergeCell ref="E41:E43"/>
+    <mergeCell ref="F41:F43"/>
+    <mergeCell ref="G41:G43"/>
+    <mergeCell ref="B38:B40"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="D38:D40"/>
+    <mergeCell ref="E38:E40"/>
+    <mergeCell ref="F38:F40"/>
+    <mergeCell ref="G38:G40"/>
+    <mergeCell ref="B47:B49"/>
+    <mergeCell ref="C47:C49"/>
+    <mergeCell ref="D47:D49"/>
+    <mergeCell ref="E47:E49"/>
+    <mergeCell ref="F47:F49"/>
+    <mergeCell ref="G47:G49"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="C44:C46"/>
+    <mergeCell ref="D44:D46"/>
+    <mergeCell ref="E44:E46"/>
+    <mergeCell ref="F44:F46"/>
+    <mergeCell ref="G44:G46"/>
+    <mergeCell ref="B53:B55"/>
+    <mergeCell ref="C53:C55"/>
+    <mergeCell ref="D53:D55"/>
+    <mergeCell ref="E53:E55"/>
+    <mergeCell ref="F53:F55"/>
+    <mergeCell ref="G53:G55"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="D50:D52"/>
+    <mergeCell ref="E50:E52"/>
+    <mergeCell ref="F50:F52"/>
+    <mergeCell ref="G50:G52"/>
+    <mergeCell ref="B59:B61"/>
+    <mergeCell ref="C59:C61"/>
+    <mergeCell ref="D59:D61"/>
+    <mergeCell ref="E59:E61"/>
+    <mergeCell ref="F59:F61"/>
+    <mergeCell ref="G59:G61"/>
+    <mergeCell ref="B56:B58"/>
+    <mergeCell ref="C56:C58"/>
+    <mergeCell ref="D56:D58"/>
+    <mergeCell ref="E56:E58"/>
+    <mergeCell ref="F56:F58"/>
+    <mergeCell ref="G56:G58"/>
+    <mergeCell ref="B65:B67"/>
+    <mergeCell ref="C65:C67"/>
+    <mergeCell ref="D65:D67"/>
+    <mergeCell ref="E65:E67"/>
+    <mergeCell ref="F65:F67"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="B62:B64"/>
+    <mergeCell ref="C62:C64"/>
+    <mergeCell ref="D62:D64"/>
+    <mergeCell ref="E62:E64"/>
+    <mergeCell ref="F62:F64"/>
+    <mergeCell ref="G62:G64"/>
+    <mergeCell ref="B71:B73"/>
+    <mergeCell ref="C71:C73"/>
+    <mergeCell ref="D71:D73"/>
+    <mergeCell ref="E71:E73"/>
+    <mergeCell ref="F71:F73"/>
+    <mergeCell ref="G71:G73"/>
+    <mergeCell ref="B68:B70"/>
+    <mergeCell ref="C68:C70"/>
+    <mergeCell ref="D68:D70"/>
+    <mergeCell ref="E68:E70"/>
+    <mergeCell ref="F68:F70"/>
+    <mergeCell ref="G68:G70"/>
+    <mergeCell ref="B77:B79"/>
+    <mergeCell ref="C77:C79"/>
+    <mergeCell ref="D77:D79"/>
+    <mergeCell ref="E77:E79"/>
+    <mergeCell ref="F77:F79"/>
+    <mergeCell ref="G77:G79"/>
+    <mergeCell ref="B74:B76"/>
+    <mergeCell ref="C74:C76"/>
+    <mergeCell ref="D74:D76"/>
+    <mergeCell ref="E74:E76"/>
+    <mergeCell ref="F74:F76"/>
+    <mergeCell ref="G74:G76"/>
+    <mergeCell ref="B83:B85"/>
+    <mergeCell ref="C83:C85"/>
+    <mergeCell ref="D83:D85"/>
+    <mergeCell ref="E83:E85"/>
+    <mergeCell ref="F83:F85"/>
+    <mergeCell ref="G83:G85"/>
+    <mergeCell ref="B80:B82"/>
+    <mergeCell ref="C80:C82"/>
+    <mergeCell ref="D80:D82"/>
+    <mergeCell ref="E80:E82"/>
+    <mergeCell ref="F80:F82"/>
+    <mergeCell ref="G80:G82"/>
+    <mergeCell ref="B89:B91"/>
+    <mergeCell ref="C89:C91"/>
+    <mergeCell ref="D89:D91"/>
+    <mergeCell ref="E89:E91"/>
+    <mergeCell ref="F89:F91"/>
+    <mergeCell ref="G89:G91"/>
+    <mergeCell ref="B86:B88"/>
+    <mergeCell ref="C86:C88"/>
+    <mergeCell ref="D86:D88"/>
+    <mergeCell ref="E86:E88"/>
+    <mergeCell ref="F86:F88"/>
+    <mergeCell ref="G86:G88"/>
+    <mergeCell ref="B95:B97"/>
+    <mergeCell ref="C95:C97"/>
+    <mergeCell ref="D95:D97"/>
+    <mergeCell ref="E95:E97"/>
+    <mergeCell ref="F95:F97"/>
+    <mergeCell ref="G95:G97"/>
+    <mergeCell ref="B92:B94"/>
+    <mergeCell ref="C92:C94"/>
+    <mergeCell ref="D92:D94"/>
+    <mergeCell ref="E92:E94"/>
+    <mergeCell ref="F92:F94"/>
+    <mergeCell ref="G92:G94"/>
+    <mergeCell ref="B101:B103"/>
+    <mergeCell ref="C101:C103"/>
+    <mergeCell ref="D101:D103"/>
+    <mergeCell ref="E101:E103"/>
+    <mergeCell ref="F101:F103"/>
+    <mergeCell ref="G101:G103"/>
+    <mergeCell ref="B98:B100"/>
+    <mergeCell ref="C98:C100"/>
+    <mergeCell ref="D98:D100"/>
+    <mergeCell ref="E98:E100"/>
+    <mergeCell ref="F98:F100"/>
+    <mergeCell ref="G98:G100"/>
+    <mergeCell ref="B107:B109"/>
+    <mergeCell ref="C107:C109"/>
+    <mergeCell ref="D107:D109"/>
+    <mergeCell ref="E107:E109"/>
+    <mergeCell ref="F107:F109"/>
+    <mergeCell ref="G107:G109"/>
+    <mergeCell ref="B104:B106"/>
+    <mergeCell ref="C104:C106"/>
+    <mergeCell ref="D104:D106"/>
+    <mergeCell ref="E104:E106"/>
+    <mergeCell ref="F104:F106"/>
+    <mergeCell ref="G104:G106"/>
+    <mergeCell ref="B113:B115"/>
+    <mergeCell ref="C113:C115"/>
+    <mergeCell ref="D113:D115"/>
+    <mergeCell ref="E113:E115"/>
+    <mergeCell ref="F113:F115"/>
+    <mergeCell ref="G113:G115"/>
+    <mergeCell ref="B110:B112"/>
+    <mergeCell ref="C110:C112"/>
+    <mergeCell ref="D110:D112"/>
+    <mergeCell ref="E110:E112"/>
+    <mergeCell ref="F110:F112"/>
+    <mergeCell ref="G110:G112"/>
+    <mergeCell ref="B119:B121"/>
+    <mergeCell ref="C119:C121"/>
+    <mergeCell ref="D119:D121"/>
+    <mergeCell ref="E119:E121"/>
+    <mergeCell ref="F119:F121"/>
+    <mergeCell ref="G119:G121"/>
+    <mergeCell ref="B116:B118"/>
+    <mergeCell ref="C116:C118"/>
+    <mergeCell ref="D116:D118"/>
+    <mergeCell ref="E116:E118"/>
+    <mergeCell ref="F116:F118"/>
+    <mergeCell ref="G116:G118"/>
+    <mergeCell ref="B125:B127"/>
+    <mergeCell ref="C125:C127"/>
+    <mergeCell ref="D125:D127"/>
+    <mergeCell ref="E125:E127"/>
+    <mergeCell ref="F125:F127"/>
+    <mergeCell ref="G125:G127"/>
+    <mergeCell ref="B122:B124"/>
+    <mergeCell ref="C122:C124"/>
+    <mergeCell ref="D122:D124"/>
+    <mergeCell ref="E122:E124"/>
+    <mergeCell ref="F122:F124"/>
+    <mergeCell ref="G122:G124"/>
+    <mergeCell ref="B131:B133"/>
+    <mergeCell ref="C131:C133"/>
+    <mergeCell ref="D131:D133"/>
+    <mergeCell ref="E131:E133"/>
+    <mergeCell ref="F131:F133"/>
+    <mergeCell ref="G131:G133"/>
+    <mergeCell ref="B128:B130"/>
+    <mergeCell ref="C128:C130"/>
+    <mergeCell ref="D128:D130"/>
+    <mergeCell ref="E128:E130"/>
+    <mergeCell ref="F128:F130"/>
+    <mergeCell ref="G128:G130"/>
+    <mergeCell ref="B137:B139"/>
+    <mergeCell ref="C137:C139"/>
+    <mergeCell ref="D137:D139"/>
+    <mergeCell ref="E137:E139"/>
+    <mergeCell ref="F137:F139"/>
+    <mergeCell ref="G137:G139"/>
+    <mergeCell ref="B134:B136"/>
+    <mergeCell ref="C134:C136"/>
+    <mergeCell ref="D134:D136"/>
+    <mergeCell ref="E134:E136"/>
+    <mergeCell ref="F134:F136"/>
+    <mergeCell ref="G134:G136"/>
     <mergeCell ref="B143:B145"/>
     <mergeCell ref="C143:C145"/>
     <mergeCell ref="D143:D145"/>
@@ -5743,382 +11597,152 @@
     <mergeCell ref="E140:E142"/>
     <mergeCell ref="F140:F142"/>
     <mergeCell ref="G140:G142"/>
-    <mergeCell ref="B137:B139"/>
-    <mergeCell ref="C137:C139"/>
-    <mergeCell ref="D137:D139"/>
-    <mergeCell ref="E137:E139"/>
-    <mergeCell ref="F137:F139"/>
-    <mergeCell ref="G137:G139"/>
-    <mergeCell ref="B134:B136"/>
-    <mergeCell ref="C134:C136"/>
-    <mergeCell ref="D134:D136"/>
-    <mergeCell ref="E134:E136"/>
-    <mergeCell ref="F134:F136"/>
-    <mergeCell ref="G134:G136"/>
-    <mergeCell ref="B131:B133"/>
-    <mergeCell ref="C131:C133"/>
-    <mergeCell ref="D131:D133"/>
-    <mergeCell ref="E131:E133"/>
-    <mergeCell ref="F131:F133"/>
-    <mergeCell ref="G131:G133"/>
-    <mergeCell ref="B128:B130"/>
-    <mergeCell ref="C128:C130"/>
-    <mergeCell ref="D128:D130"/>
-    <mergeCell ref="E128:E130"/>
-    <mergeCell ref="F128:F130"/>
-    <mergeCell ref="G128:G130"/>
-    <mergeCell ref="B125:B127"/>
-    <mergeCell ref="C125:C127"/>
-    <mergeCell ref="D125:D127"/>
-    <mergeCell ref="E125:E127"/>
-    <mergeCell ref="F125:F127"/>
-    <mergeCell ref="G125:G127"/>
-    <mergeCell ref="B122:B124"/>
-    <mergeCell ref="C122:C124"/>
-    <mergeCell ref="D122:D124"/>
-    <mergeCell ref="E122:E124"/>
-    <mergeCell ref="F122:F124"/>
-    <mergeCell ref="G122:G124"/>
-    <mergeCell ref="B119:B121"/>
-    <mergeCell ref="C119:C121"/>
-    <mergeCell ref="D119:D121"/>
-    <mergeCell ref="E119:E121"/>
-    <mergeCell ref="F119:F121"/>
-    <mergeCell ref="G119:G121"/>
-    <mergeCell ref="B116:B118"/>
-    <mergeCell ref="C116:C118"/>
-    <mergeCell ref="D116:D118"/>
-    <mergeCell ref="E116:E118"/>
-    <mergeCell ref="F116:F118"/>
-    <mergeCell ref="G116:G118"/>
-    <mergeCell ref="B113:B115"/>
-    <mergeCell ref="C113:C115"/>
-    <mergeCell ref="D113:D115"/>
-    <mergeCell ref="E113:E115"/>
-    <mergeCell ref="F113:F115"/>
-    <mergeCell ref="G113:G115"/>
-    <mergeCell ref="B110:B112"/>
-    <mergeCell ref="C110:C112"/>
-    <mergeCell ref="D110:D112"/>
-    <mergeCell ref="E110:E112"/>
-    <mergeCell ref="F110:F112"/>
-    <mergeCell ref="G110:G112"/>
-    <mergeCell ref="B107:B109"/>
-    <mergeCell ref="C107:C109"/>
-    <mergeCell ref="D107:D109"/>
-    <mergeCell ref="E107:E109"/>
-    <mergeCell ref="F107:F109"/>
-    <mergeCell ref="G107:G109"/>
-    <mergeCell ref="B104:B106"/>
-    <mergeCell ref="C104:C106"/>
-    <mergeCell ref="D104:D106"/>
-    <mergeCell ref="E104:E106"/>
-    <mergeCell ref="F104:F106"/>
-    <mergeCell ref="G104:G106"/>
-    <mergeCell ref="B101:B103"/>
-    <mergeCell ref="C101:C103"/>
-    <mergeCell ref="D101:D103"/>
-    <mergeCell ref="E101:E103"/>
-    <mergeCell ref="F101:F103"/>
-    <mergeCell ref="G101:G103"/>
-    <mergeCell ref="B98:B100"/>
-    <mergeCell ref="C98:C100"/>
-    <mergeCell ref="D98:D100"/>
-    <mergeCell ref="E98:E100"/>
-    <mergeCell ref="F98:F100"/>
-    <mergeCell ref="G98:G100"/>
-    <mergeCell ref="B95:B97"/>
-    <mergeCell ref="C95:C97"/>
-    <mergeCell ref="D95:D97"/>
-    <mergeCell ref="E95:E97"/>
-    <mergeCell ref="F95:F97"/>
-    <mergeCell ref="G95:G97"/>
-    <mergeCell ref="B92:B94"/>
-    <mergeCell ref="C92:C94"/>
-    <mergeCell ref="D92:D94"/>
-    <mergeCell ref="E92:E94"/>
-    <mergeCell ref="F92:F94"/>
-    <mergeCell ref="G92:G94"/>
-    <mergeCell ref="B89:B91"/>
-    <mergeCell ref="C89:C91"/>
-    <mergeCell ref="D89:D91"/>
-    <mergeCell ref="E89:E91"/>
-    <mergeCell ref="F89:F91"/>
-    <mergeCell ref="G89:G91"/>
-    <mergeCell ref="B86:B88"/>
-    <mergeCell ref="C86:C88"/>
-    <mergeCell ref="D86:D88"/>
-    <mergeCell ref="E86:E88"/>
-    <mergeCell ref="F86:F88"/>
-    <mergeCell ref="G86:G88"/>
-    <mergeCell ref="B83:B85"/>
-    <mergeCell ref="C83:C85"/>
-    <mergeCell ref="D83:D85"/>
-    <mergeCell ref="E83:E85"/>
-    <mergeCell ref="F83:F85"/>
-    <mergeCell ref="G83:G85"/>
-    <mergeCell ref="B80:B82"/>
-    <mergeCell ref="C80:C82"/>
-    <mergeCell ref="D80:D82"/>
-    <mergeCell ref="E80:E82"/>
-    <mergeCell ref="F80:F82"/>
-    <mergeCell ref="G80:G82"/>
-    <mergeCell ref="B77:B79"/>
-    <mergeCell ref="C77:C79"/>
-    <mergeCell ref="D77:D79"/>
-    <mergeCell ref="E77:E79"/>
-    <mergeCell ref="F77:F79"/>
-    <mergeCell ref="G77:G79"/>
-    <mergeCell ref="B74:B76"/>
-    <mergeCell ref="C74:C76"/>
-    <mergeCell ref="D74:D76"/>
-    <mergeCell ref="E74:E76"/>
-    <mergeCell ref="F74:F76"/>
-    <mergeCell ref="G74:G76"/>
-    <mergeCell ref="B71:B73"/>
-    <mergeCell ref="C71:C73"/>
-    <mergeCell ref="D71:D73"/>
-    <mergeCell ref="E71:E73"/>
-    <mergeCell ref="F71:F73"/>
-    <mergeCell ref="G71:G73"/>
-    <mergeCell ref="B68:B70"/>
-    <mergeCell ref="C68:C70"/>
-    <mergeCell ref="D68:D70"/>
-    <mergeCell ref="E68:E70"/>
-    <mergeCell ref="F68:F70"/>
-    <mergeCell ref="G68:G70"/>
-    <mergeCell ref="B65:B67"/>
-    <mergeCell ref="C65:C67"/>
-    <mergeCell ref="D65:D67"/>
-    <mergeCell ref="E65:E67"/>
-    <mergeCell ref="F65:F67"/>
-    <mergeCell ref="G65:G67"/>
-    <mergeCell ref="B62:B64"/>
-    <mergeCell ref="C62:C64"/>
-    <mergeCell ref="D62:D64"/>
-    <mergeCell ref="E62:E64"/>
-    <mergeCell ref="F62:F64"/>
-    <mergeCell ref="G62:G64"/>
-    <mergeCell ref="B59:B61"/>
-    <mergeCell ref="C59:C61"/>
-    <mergeCell ref="D59:D61"/>
-    <mergeCell ref="E59:E61"/>
-    <mergeCell ref="F59:F61"/>
-    <mergeCell ref="G59:G61"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="C56:C58"/>
-    <mergeCell ref="D56:D58"/>
-    <mergeCell ref="E56:E58"/>
-    <mergeCell ref="F56:F58"/>
-    <mergeCell ref="G56:G58"/>
-    <mergeCell ref="B53:B55"/>
-    <mergeCell ref="C53:C55"/>
-    <mergeCell ref="D53:D55"/>
-    <mergeCell ref="E53:E55"/>
-    <mergeCell ref="F53:F55"/>
-    <mergeCell ref="G53:G55"/>
-    <mergeCell ref="B50:B52"/>
-    <mergeCell ref="C50:C52"/>
-    <mergeCell ref="D50:D52"/>
-    <mergeCell ref="E50:E52"/>
-    <mergeCell ref="F50:F52"/>
-    <mergeCell ref="G50:G52"/>
-    <mergeCell ref="B47:B49"/>
-    <mergeCell ref="C47:C49"/>
-    <mergeCell ref="D47:D49"/>
-    <mergeCell ref="E47:E49"/>
-    <mergeCell ref="F47:F49"/>
-    <mergeCell ref="G47:G49"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="C44:C46"/>
-    <mergeCell ref="D44:D46"/>
-    <mergeCell ref="E44:E46"/>
-    <mergeCell ref="F44:F46"/>
-    <mergeCell ref="G44:G46"/>
-    <mergeCell ref="B41:B43"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="D41:D43"/>
-    <mergeCell ref="E41:E43"/>
-    <mergeCell ref="F41:F43"/>
-    <mergeCell ref="G41:G43"/>
-    <mergeCell ref="B38:B40"/>
-    <mergeCell ref="C38:C40"/>
-    <mergeCell ref="D38:D40"/>
-    <mergeCell ref="E38:E40"/>
-    <mergeCell ref="F38:F40"/>
-    <mergeCell ref="G38:G40"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:C37"/>
-    <mergeCell ref="D35:D37"/>
-    <mergeCell ref="E35:E37"/>
-    <mergeCell ref="F35:F37"/>
-    <mergeCell ref="G35:G37"/>
-    <mergeCell ref="B32:B34"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="E32:E34"/>
-    <mergeCell ref="F32:F34"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="B29:B31"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="D29:D31"/>
-    <mergeCell ref="E29:E31"/>
-    <mergeCell ref="F29:F31"/>
-    <mergeCell ref="G29:G31"/>
-    <mergeCell ref="B26:B28"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="D26:D28"/>
-    <mergeCell ref="E26:E28"/>
-    <mergeCell ref="F26:F28"/>
-    <mergeCell ref="G26:G28"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="D23:D25"/>
-    <mergeCell ref="E23:E25"/>
-    <mergeCell ref="F23:F25"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="F20:F22"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="D17:D19"/>
-    <mergeCell ref="E17:E19"/>
-    <mergeCell ref="F17:F19"/>
-    <mergeCell ref="G17:G19"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="E11:E13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="G11:G13"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="G8:G10"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="F5:F7"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="G2:G4"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A4" r:id="rId1" tooltip="Jacob Duffy" display="https://www.espncricinfo.com/cricketers/jacob-duffy-547766" xr:uid="{5102CBA7-3B59-4ED9-AAA7-408AC1DEE0DF}"/>
-    <hyperlink ref="B2" r:id="rId2" tooltip="RCB" display="https://www.espncricinfo.com/team/royal-challengers-bengaluru-335970" xr:uid="{9B1024DA-E8A3-4295-B18E-32A45765F8BC}"/>
-    <hyperlink ref="A7" r:id="rId3" tooltip="Ishan Kishan" display="https://www.espncricinfo.com/cricketers/ishan-kishan-720471" xr:uid="{AFC843E6-24EF-48F1-BE85-29142D623F60}"/>
-    <hyperlink ref="B5" r:id="rId4" tooltip="SRH" display="https://www.espncricinfo.com/team/sunrisers-hyderabad-628333" xr:uid="{2E49D3D2-EA9B-4D5D-B562-283993A66B77}"/>
-    <hyperlink ref="A10" r:id="rId5" tooltip="Shardul Thakur" display="https://www.espncricinfo.com/cricketers/shardul-thakur-475281" xr:uid="{C2AB01A2-94DC-4957-84B5-F7626DEE3907}"/>
-    <hyperlink ref="B8" r:id="rId6" tooltip="MI" display="https://www.espncricinfo.com/team/mumbai-indians-335978" xr:uid="{E57C9797-BFF6-44BA-BD3F-B33CB5A76736}"/>
-    <hyperlink ref="A13" r:id="rId7" tooltip="Rohit Sharma" display="https://www.espncricinfo.com/cricketers/rohit-sharma-34102" xr:uid="{5501F197-E95A-452C-8949-BB3BDA761226}"/>
-    <hyperlink ref="B11" r:id="rId8" tooltip="MI" display="https://www.espncricinfo.com/team/mumbai-indians-335978" xr:uid="{C139EA82-0ABF-41AE-871A-A180882B4968}"/>
-    <hyperlink ref="A16" r:id="rId9" tooltip="Ryan Rickelton" display="https://www.espncricinfo.com/cricketers/ryan-rickelton-605661" xr:uid="{1C793A8D-5AD5-43F5-ADD2-A4BE6745F097}"/>
-    <hyperlink ref="B14" r:id="rId10" tooltip="MI" display="https://www.espncricinfo.com/team/mumbai-indians-335978" xr:uid="{7C4904F6-172C-4C18-B846-596B52CCE261}"/>
-    <hyperlink ref="A19" r:id="rId11" tooltip="Devdutt Padikkal" display="https://www.espncricinfo.com/cricketers/devdutt-padikkal-1119026" xr:uid="{7F70CAD8-6291-4B25-B73E-E473328B8BF4}"/>
-    <hyperlink ref="B17" r:id="rId12" tooltip="RCB" display="https://www.espncricinfo.com/team/royal-challengers-bengaluru-335970" xr:uid="{FABA9309-4D7F-4CC7-9ADF-BDFFE7F10071}"/>
-    <hyperlink ref="A22" r:id="rId13" tooltip="Aniket Verma" display="https://www.espncricinfo.com/cricketers/aniket-verma-1409976" xr:uid="{39B4F939-B937-46F1-BCE4-1AB6669456D3}"/>
-    <hyperlink ref="B20" r:id="rId14" tooltip="SRH" display="https://www.espncricinfo.com/team/sunrisers-hyderabad-628333" xr:uid="{0876A675-2024-4A4E-B9F7-A4F5BF613B8B}"/>
-    <hyperlink ref="A25" r:id="rId15" tooltip="Virat Kohli" display="https://www.espncricinfo.com/cricketers/virat-kohli-253802" xr:uid="{ACC96CCE-5E5C-4FCB-8A2E-611003BF4097}"/>
-    <hyperlink ref="B23" r:id="rId16" tooltip="RCB" display="https://www.espncricinfo.com/team/royal-challengers-bengaluru-335970" xr:uid="{7815B2BF-09C8-408C-9E06-8AC4B4C370CC}"/>
-    <hyperlink ref="A28" r:id="rId17" tooltip="Kartik Tyagi" display="https://www.espncricinfo.com/cricketers/kartik-tyagi-1122918" xr:uid="{C0EB153D-4794-4A04-9F56-9D0209A31A27}"/>
-    <hyperlink ref="B26" r:id="rId18" tooltip="KKR" display="https://www.espncricinfo.com/team/kolkata-knight-riders-335971" xr:uid="{CB5EB893-9103-457A-BF6F-42875C0D5798}"/>
-    <hyperlink ref="A31" r:id="rId19" tooltip="Romario Shepherd" display="https://www.espncricinfo.com/cricketers/romario-shepherd-677077" xr:uid="{FE0F8876-3C8F-4763-9F2C-D145FFAA41EC}"/>
-    <hyperlink ref="B29" r:id="rId20" tooltip="RCB" display="https://www.espncricinfo.com/team/royal-challengers-bengaluru-335970" xr:uid="{EA0DAE33-F8B5-4518-9253-1EEDEEADE917}"/>
-    <hyperlink ref="A34" r:id="rId21" tooltip="Ajinkya Rahane" display="https://www.espncricinfo.com/cricketers/ajinkya-rahane-277916" xr:uid="{3CCE097B-F03E-4467-B4D7-AA5F0BBCC417}"/>
-    <hyperlink ref="B32" r:id="rId22" tooltip="KKR" display="https://www.espncricinfo.com/team/kolkata-knight-riders-335971" xr:uid="{B6743C3C-35C1-48A5-A41E-10F85DC48333}"/>
-    <hyperlink ref="A37" r:id="rId23" tooltip="Finn Allen" display="https://www.espncricinfo.com/cricketers/finn-allen-959759" xr:uid="{41E14407-59E5-46D2-B574-442C2777BEF8}"/>
-    <hyperlink ref="B35" r:id="rId24" tooltip="KKR" display="https://www.espncricinfo.com/team/kolkata-knight-riders-335971" xr:uid="{F44F580B-73E7-43C3-ACC2-E703860A5E85}"/>
-    <hyperlink ref="A40" r:id="rId25" tooltip="Jaydev Unadkat" display="https://www.espncricinfo.com/cricketers/jaydev-unadkat-390484" xr:uid="{3E81DD44-0C21-4FC8-921B-9A0CF27237D8}"/>
-    <hyperlink ref="B38" r:id="rId26" tooltip="SRH" display="https://www.espncricinfo.com/team/sunrisers-hyderabad-628333" xr:uid="{1287CB0C-C8C2-432D-B9D3-45D7511F6A3B}"/>
-    <hyperlink ref="A43" r:id="rId27" tooltip="Suyash Sharma" display="https://www.espncricinfo.com/cricketers/suyash-sharma-1350792" xr:uid="{F02170E1-936A-480C-8F49-AFC696B151F4}"/>
-    <hyperlink ref="B41" r:id="rId28" tooltip="RCB" display="https://www.espncricinfo.com/team/royal-challengers-bengaluru-335970" xr:uid="{6E4C3CDD-E867-4140-ACF3-AA1EAE05770F}"/>
-    <hyperlink ref="A46" r:id="rId29" tooltip="Angkrish Raghuvanshi" display="https://www.espncricinfo.com/cricketers/angkrish-raghuvanshi-1292495" xr:uid="{9C071657-EF29-47C3-8159-777C0914CC5E}"/>
-    <hyperlink ref="B44" r:id="rId30" tooltip="KKR" display="https://www.espncricinfo.com/team/kolkata-knight-riders-335971" xr:uid="{E0D3DAA9-04B5-4307-8F2B-36349068F1C2}"/>
-    <hyperlink ref="A49" r:id="rId31" tooltip="Hardik Pandya" display="https://www.espncricinfo.com/cricketers/hardik-pandya-625371" xr:uid="{5072F2AC-965C-4839-B9BD-F2E0D8517370}"/>
-    <hyperlink ref="B47" r:id="rId32" tooltip="MI" display="https://www.espncricinfo.com/team/mumbai-indians-335978" xr:uid="{7D005A13-C180-4F31-82B9-652484CFD506}"/>
-    <hyperlink ref="A52" r:id="rId33" tooltip="Bhuvneshwar Kumar" display="https://www.espncricinfo.com/cricketers/bhuvneshwar-kumar-326016" xr:uid="{9933523E-1170-4F12-9295-EA6985C18D49}"/>
-    <hyperlink ref="B50" r:id="rId34" tooltip="RCB" display="https://www.espncricinfo.com/team/royal-challengers-bengaluru-335970" xr:uid="{6F987F9E-AF91-4F0C-8D01-FF3CF91187C7}"/>
-    <hyperlink ref="A55" r:id="rId35" tooltip="David Payne" display="https://www.espncricinfo.com/cricketers/david-payne-362710" xr:uid="{0ABBBF31-D9E8-405B-A44B-B2AEA6F7D93D}"/>
-    <hyperlink ref="B53" r:id="rId36" tooltip="SRH" display="https://www.espncricinfo.com/team/sunrisers-hyderabad-628333" xr:uid="{5A57CC0B-1085-4BFE-ACCC-429A9BFB4A13}"/>
-    <hyperlink ref="A58" r:id="rId37" tooltip="Jasprit Bumrah" display="https://www.espncricinfo.com/cricketers/jasprit-bumrah-625383" xr:uid="{3ED93B91-9FEE-4858-9577-8F8D9683C45D}"/>
-    <hyperlink ref="B56" r:id="rId38" tooltip="MI" display="https://www.espncricinfo.com/team/mumbai-indians-335978" xr:uid="{7731CDA1-715F-4891-A1A2-EFB6F6F88F43}"/>
-    <hyperlink ref="A61" r:id="rId39" tooltip="Vaibhav Arora" display="https://www.espncricinfo.com/cricketers/vaibhav-arora-1209292" xr:uid="{DB9CA555-A9B7-4EFB-B01D-2C51D8F54D55}"/>
-    <hyperlink ref="B59" r:id="rId40" tooltip="KKR" display="https://www.espncricinfo.com/team/kolkata-knight-riders-335971" xr:uid="{724CEC30-B707-4273-B957-C74302071B18}"/>
-    <hyperlink ref="A64" r:id="rId41" tooltip="Sunil Narine" display="https://www.espncricinfo.com/cricketers/sunil-narine-230558" xr:uid="{72763EBC-ACCA-48AD-A2F0-E28D0C828C7E}"/>
-    <hyperlink ref="B62" r:id="rId42" tooltip="KKR" display="https://www.espncricinfo.com/team/kolkata-knight-riders-335971" xr:uid="{FE2AFD59-8DDB-4866-A3D1-BC150C9F8A71}"/>
-    <hyperlink ref="A67" r:id="rId43" tooltip="Rajat Patidar" display="https://www.espncricinfo.com/cricketers/rajat-patidar-823703" xr:uid="{4906AFC5-E5A7-42A0-86AD-9D6F2731DE6C}"/>
-    <hyperlink ref="B65" r:id="rId44" tooltip="RCB" display="https://www.espncricinfo.com/team/royal-challengers-bengaluru-335970" xr:uid="{2A2D2861-15EC-4198-8419-BBB7A34701B3}"/>
-    <hyperlink ref="A70" r:id="rId45" tooltip="Harsh Dubey" display="https://www.espncricinfo.com/cricketers/harsh-dubey-1216159" xr:uid="{7A858393-8890-497B-92F7-09F147F8CB0D}"/>
-    <hyperlink ref="B68" r:id="rId46" tooltip="SRH" display="https://www.espncricinfo.com/team/sunrisers-hyderabad-628333" xr:uid="{98C23E17-5C47-4B25-A9E1-337C95A72D36}"/>
-    <hyperlink ref="A73" r:id="rId47" tooltip="Trent Boult" display="https://www.espncricinfo.com/cricketers/trent-boult-277912" xr:uid="{529162A7-AB43-4808-BCE2-5654671067F1}"/>
-    <hyperlink ref="B71" r:id="rId48" tooltip="MI" display="https://www.espncricinfo.com/team/mumbai-indians-335978" xr:uid="{91264812-8966-4D10-A8A5-A2786CA335A3}"/>
-    <hyperlink ref="A76" r:id="rId49" tooltip="Abhinandan Singh" display="https://www.espncricinfo.com/cricketers/abhinandan-singh-1449085" xr:uid="{3E0C6190-A371-4DBC-9001-27D7E7C5D963}"/>
-    <hyperlink ref="B74" r:id="rId50" tooltip="RCB" display="https://www.espncricinfo.com/team/royal-challengers-bengaluru-335970" xr:uid="{696174DB-18BC-4EB7-BD64-66C63965FF72}"/>
-    <hyperlink ref="A79" r:id="rId51" tooltip="Suryakumar Yadav" display="https://www.espncricinfo.com/cricketers/suryakumar-yadav-446507" xr:uid="{B1F67F00-7603-4038-95BC-591FA108B5C1}"/>
-    <hyperlink ref="B77" r:id="rId52" tooltip="MI" display="https://www.espncricinfo.com/team/mumbai-indians-335978" xr:uid="{8CA93CFB-8486-4236-97B5-28F237752086}"/>
-    <hyperlink ref="A82" r:id="rId53" tooltip="Heinrich Klaasen" display="https://www.espncricinfo.com/cricketers/heinrich-klaasen-436757" xr:uid="{790FEB1C-FE13-4163-B05B-03528E48981A}"/>
-    <hyperlink ref="B80" r:id="rId54" tooltip="SRH" display="https://www.espncricinfo.com/team/sunrisers-hyderabad-628333" xr:uid="{6B401054-7CB6-4ACF-9C53-3B1DB483DC38}"/>
-    <hyperlink ref="A85" r:id="rId55" tooltip="Tilak Varma" display="https://www.espncricinfo.com/cricketers/tilak-varma-1170265" xr:uid="{4F4021A8-9B35-456A-8A89-C6D71A85BD53}"/>
-    <hyperlink ref="B83" r:id="rId56" tooltip="MI" display="https://www.espncricinfo.com/team/mumbai-indians-335978" xr:uid="{69F5FB77-731C-458D-B6DC-82AFD926BC66}"/>
-    <hyperlink ref="A88" r:id="rId57" tooltip="Cameron Green" display="https://www.espncricinfo.com/cricketers/cameron-green-1076713" xr:uid="{05E45FAD-278A-4055-B390-729BBBD66D0F}"/>
-    <hyperlink ref="B86" r:id="rId58" tooltip="KKR" display="https://www.espncricinfo.com/team/kolkata-knight-riders-335971" xr:uid="{75FA870B-C035-4809-B9B4-82F06AF2B7E5}"/>
-    <hyperlink ref="A91" r:id="rId59" tooltip="Tim David" display="https://www.espncricinfo.com/cricketers/tim-david-892749" xr:uid="{3654C3BB-F2AD-4344-97A5-C364B510595F}"/>
-    <hyperlink ref="B89" r:id="rId60" tooltip="RCB" display="https://www.espncricinfo.com/team/royal-challengers-bengaluru-335970" xr:uid="{FBB9EFA3-812A-4F38-89CE-FD1291EBBB91}"/>
-    <hyperlink ref="A94" r:id="rId61" tooltip="Blessing Muzarabani" display="https://www.espncricinfo.com/cricketers/blessing-muzarabani-827051" xr:uid="{EEDF9A17-48BD-4F53-8BE9-76B4D4A43B80}"/>
-    <hyperlink ref="B92" r:id="rId62" tooltip="KKR" display="https://www.espncricinfo.com/team/kolkata-knight-riders-335971" xr:uid="{C5C2BEF6-A419-4981-9979-ECA87CA199FF}"/>
-    <hyperlink ref="A97" r:id="rId63" tooltip="Rinku Singh" display="https://www.espncricinfo.com/cricketers/rinku-singh-723105" xr:uid="{10E7C424-0C25-431F-8A20-849EBD6E5799}"/>
-    <hyperlink ref="B95" r:id="rId64" tooltip="KKR" display="https://www.espncricinfo.com/team/kolkata-knight-riders-335971" xr:uid="{03B4A735-EA71-4659-9988-3A618FB64F9F}"/>
-    <hyperlink ref="A100" r:id="rId65" tooltip="Varun Chakravarthy" display="https://www.espncricinfo.com/cricketers/varun-chakravarthy-1108375" xr:uid="{DE047749-DC07-4520-80A3-D3F770C2FCFE}"/>
-    <hyperlink ref="B98" r:id="rId66" tooltip="KKR" display="https://www.espncricinfo.com/team/kolkata-knight-riders-335971" xr:uid="{969054B1-83A1-493F-80B5-A7B4F6DDF6F2}"/>
-    <hyperlink ref="A103" r:id="rId67" tooltip="Salil Arora" display="https://www.espncricinfo.com/cricketers/salil-arora-1199281" xr:uid="{B14C8188-92B3-456E-A3A8-C8DAC73D92A6}"/>
-    <hyperlink ref="B101" r:id="rId68" tooltip="SRH" display="https://www.espncricinfo.com/team/sunrisers-hyderabad-628333" xr:uid="{7A46EBBC-0A38-41EA-8C4A-F25511C48E3B}"/>
-    <hyperlink ref="A106" r:id="rId69" tooltip="Naman Dhir" display="https://www.espncricinfo.com/cricketers/naman-dhir-1287032" xr:uid="{AE3783E7-BE23-4E6D-BF5F-5CE8802E7438}"/>
-    <hyperlink ref="B104" r:id="rId70" tooltip="MI" display="https://www.espncricinfo.com/team/mumbai-indians-335978" xr:uid="{8EC137A9-FC06-4703-9F77-F80681E08883}"/>
-    <hyperlink ref="A109" r:id="rId71" tooltip="Travis Head" display="https://www.espncricinfo.com/cricketers/travis-head-530011" xr:uid="{BBAD8B25-1D45-4858-B599-ED9D039B1AC2}"/>
-    <hyperlink ref="B107" r:id="rId72" tooltip="SRH" display="https://www.espncricinfo.com/team/sunrisers-hyderabad-628333" xr:uid="{11C6DD53-E283-4369-9EEC-5AC6DF0C83AD}"/>
-    <hyperlink ref="A112" r:id="rId73" tooltip="Anukul Roy" display="https://www.espncricinfo.com/cricketers/anukul-roy-1079839" xr:uid="{EF02233B-A478-45D3-8AEE-7174CC984619}"/>
-    <hyperlink ref="B110" r:id="rId74" tooltip="KKR" display="https://www.espncricinfo.com/team/kolkata-knight-riders-335971" xr:uid="{5E199A0D-E8D3-4864-BAB5-8F0C075101E1}"/>
-    <hyperlink ref="A115" r:id="rId75" tooltip="AM Ghazanfar" display="https://www.espncricinfo.com/cricketers/am-ghazanfar-1326798" xr:uid="{59F5040C-098C-446F-8722-BCEF4984577C}"/>
-    <hyperlink ref="B113" r:id="rId76" tooltip="MI" display="https://www.espncricinfo.com/team/mumbai-indians-335978" xr:uid="{1F804637-4F4A-487D-A0DA-E770022E4897}"/>
-    <hyperlink ref="A118" r:id="rId77" tooltip="Phil Salt" display="https://www.espncricinfo.com/cricketers/phil-salt-669365" xr:uid="{9681CD27-2DE0-4DDE-809A-C5DA3A5DC5D5}"/>
-    <hyperlink ref="B116" r:id="rId78" tooltip="RCB" display="https://www.espncricinfo.com/team/royal-challengers-bengaluru-335970" xr:uid="{A2714595-B536-4B74-910B-DCFF1DFDF7B7}"/>
-    <hyperlink ref="A121" r:id="rId79" tooltip="Sherfane Rutherford" display="https://www.espncricinfo.com/cricketers/sherfane-rutherford-914541" xr:uid="{B7DD3F5B-B89F-4FD3-90A9-6D26FE8E0AE4}"/>
-    <hyperlink ref="B119" r:id="rId80" tooltip="MI" display="https://www.espncricinfo.com/team/mumbai-indians-335978" xr:uid="{8CF4A3FB-11F4-4BC4-89DE-0CE93503DEE9}"/>
-    <hyperlink ref="A124" r:id="rId81" tooltip="Krunal Pandya" display="https://www.espncricinfo.com/cricketers/krunal-pandya-471342" xr:uid="{2A762D51-B83E-43D5-BB8D-867A9AA40CB0}"/>
-    <hyperlink ref="B122" r:id="rId82" tooltip="RCB" display="https://www.espncricinfo.com/team/royal-challengers-bengaluru-335970" xr:uid="{91BEBFB0-E380-400E-804D-044A916FA2E2}"/>
-    <hyperlink ref="A127" r:id="rId83" tooltip="Jitesh Sharma" display="https://www.espncricinfo.com/cricketers/jitesh-sharma-721867" xr:uid="{AE1B5B28-3CBA-4C95-BB16-1808C006CCEB}"/>
-    <hyperlink ref="B125" r:id="rId84" tooltip="RCB" display="https://www.espncricinfo.com/team/royal-challengers-bengaluru-335970" xr:uid="{2D259D82-0D00-4B19-88ED-7B986FA13210}"/>
-    <hyperlink ref="A130" r:id="rId85" tooltip="Harshal Patel" display="https://www.espncricinfo.com/cricketers/harshal-patel-390481" xr:uid="{5903C180-C048-4C94-94D4-07E798BE47DB}"/>
-    <hyperlink ref="B128" r:id="rId86" tooltip="SRH" display="https://www.espncricinfo.com/team/sunrisers-hyderabad-628333" xr:uid="{0B663974-29EB-455D-8DF9-848C2431252D}"/>
-    <hyperlink ref="A133" r:id="rId87" tooltip="Mayank Markande" display="https://www.espncricinfo.com/cricketers/mayank-markande-1081442" xr:uid="{ADE2F05D-D2AE-4F14-8399-02277A8D6E3D}"/>
-    <hyperlink ref="B131" r:id="rId88" tooltip="MI" display="https://www.espncricinfo.com/team/mumbai-indians-335978" xr:uid="{8A10F315-FB59-4E46-82B6-4D48097E995E}"/>
-    <hyperlink ref="A136" r:id="rId89" tooltip="Abhishek Sharma" display="https://www.espncricinfo.com/cricketers/abhishek-sharma-1070183" xr:uid="{8F234662-88CF-4A36-B11B-D58F187522AC}"/>
-    <hyperlink ref="B134" r:id="rId90" tooltip="SRH" display="https://www.espncricinfo.com/team/sunrisers-hyderabad-628333" xr:uid="{29AD3FFF-3A0A-40C0-A860-86CE26074CBB}"/>
-    <hyperlink ref="A139" r:id="rId91" tooltip="Ramandeep Singh" display="https://www.espncricinfo.com/cricketers/ramandeep-singh-1079470" xr:uid="{8BFE9374-8411-4899-9FED-1E07F20879EC}"/>
-    <hyperlink ref="B137" r:id="rId92" tooltip="KKR" display="https://www.espncricinfo.com/team/kolkata-knight-riders-335971" xr:uid="{EE2C58D1-1CC5-407E-922B-F60547E01258}"/>
-    <hyperlink ref="A142" r:id="rId93" tooltip="Nitish Kumar Reddy" display="https://www.espncricinfo.com/cricketers/nitish-kumar-reddy-1175496" xr:uid="{190DFA27-95C0-467A-AEC6-1E2970E8D0A2}"/>
-    <hyperlink ref="B140" r:id="rId94" tooltip="SRH" display="https://www.espncricinfo.com/team/sunrisers-hyderabad-628333" xr:uid="{632BF719-4EDB-4141-8618-5900688CCC91}"/>
-    <hyperlink ref="A145" r:id="rId95" tooltip="Eshan Malinga" display="https://www.espncricinfo.com/cricketers/eshan-malinga-1306214" xr:uid="{6A256B99-D909-4105-9173-F5B35D51ED16}"/>
-    <hyperlink ref="B143" r:id="rId96" tooltip="SRH" display="https://www.espncricinfo.com/team/sunrisers-hyderabad-628333" xr:uid="{170CE189-AC51-49CD-BA04-C501747B6456}"/>
+    <hyperlink ref="A4" r:id="rId1" tooltip="Jacob Duffy" display="https://www.espncricinfo.com/cricketers/jacob-duffy-547766" xr:uid="{E11A5A2A-8BBA-4E4D-8413-ABF84E0C6C2E}"/>
+    <hyperlink ref="B2" r:id="rId2" tooltip="RCB" display="https://www.espncricinfo.com/team/royal-challengers-bengaluru-335970" xr:uid="{73C90F26-3152-40B1-BDD2-08B76A9C0DC0}"/>
+    <hyperlink ref="A7" r:id="rId3" tooltip="Ishan Kishan" display="https://www.espncricinfo.com/cricketers/ishan-kishan-720471" xr:uid="{8A234940-0D7D-43DC-85FC-67591258D3CD}"/>
+    <hyperlink ref="B5" r:id="rId4" tooltip="SRH" display="https://www.espncricinfo.com/team/sunrisers-hyderabad-628333" xr:uid="{083684C0-F1E0-48C9-9340-FF4A4908F65B}"/>
+    <hyperlink ref="A10" r:id="rId5" tooltip="Shardul Thakur" display="https://www.espncricinfo.com/cricketers/shardul-thakur-475281" xr:uid="{5020B5AC-1C42-41F7-9321-1059150C5EF5}"/>
+    <hyperlink ref="B8" r:id="rId6" tooltip="MI" display="https://www.espncricinfo.com/team/mumbai-indians-335978" xr:uid="{40247FA3-08C9-455D-BBE6-25D7999BF858}"/>
+    <hyperlink ref="A13" r:id="rId7" tooltip="Rohit Sharma" display="https://www.espncricinfo.com/cricketers/rohit-sharma-34102" xr:uid="{FA10CDB7-3A1F-459A-85CB-62DD63B33EFB}"/>
+    <hyperlink ref="B11" r:id="rId8" tooltip="MI" display="https://www.espncricinfo.com/team/mumbai-indians-335978" xr:uid="{2830F6C6-4D4E-4E7C-BF35-B9912549109E}"/>
+    <hyperlink ref="A16" r:id="rId9" tooltip="Ryan Rickelton" display="https://www.espncricinfo.com/cricketers/ryan-rickelton-605661" xr:uid="{16907D2E-0BBC-4BD4-A22E-0081FF00BD94}"/>
+    <hyperlink ref="B14" r:id="rId10" tooltip="MI" display="https://www.espncricinfo.com/team/mumbai-indians-335978" xr:uid="{F418ED54-182C-4F6B-9A12-F9624CA19CE4}"/>
+    <hyperlink ref="A19" r:id="rId11" tooltip="Devdutt Padikkal" display="https://www.espncricinfo.com/cricketers/devdutt-padikkal-1119026" xr:uid="{FC7A9AB6-5AEA-4444-B38A-7DDD3A4D0576}"/>
+    <hyperlink ref="B17" r:id="rId12" tooltip="RCB" display="https://www.espncricinfo.com/team/royal-challengers-bengaluru-335970" xr:uid="{A04E0625-D03F-42AC-8296-71EF78F1C61F}"/>
+    <hyperlink ref="A22" r:id="rId13" tooltip="Nandre Burger" display="https://www.espncricinfo.com/cricketers/nandre-burger-971349" xr:uid="{79DD2A4C-D910-4C3A-9992-A7B6BD0213D7}"/>
+    <hyperlink ref="B20" r:id="rId14" tooltip="RR" display="https://www.espncricinfo.com/team/rajasthan-royals-335977" xr:uid="{196D5E8A-7BAB-4003-9CAE-48C29507EF85}"/>
+    <hyperlink ref="A25" r:id="rId15" tooltip="Aniket Verma" display="https://www.espncricinfo.com/cricketers/aniket-verma-1409976" xr:uid="{360F9443-0FCC-46ED-A072-9F97736CE74E}"/>
+    <hyperlink ref="B23" r:id="rId16" tooltip="SRH" display="https://www.espncricinfo.com/team/sunrisers-hyderabad-628333" xr:uid="{9A42EE17-D982-4355-965C-E688C62C76A0}"/>
+    <hyperlink ref="A28" r:id="rId17" tooltip="Vaibhav Sooryavanshi" display="https://www.espncricinfo.com/cricketers/vaibhav-sooryavanshi-1408688" xr:uid="{EDC5BD4D-7FEB-4362-A258-30BDFAB11B61}"/>
+    <hyperlink ref="B26" r:id="rId18" tooltip="RR" display="https://www.espncricinfo.com/team/rajasthan-royals-335977" xr:uid="{8FA3C9E1-5870-4AE5-9E3C-B4755028052B}"/>
+    <hyperlink ref="A31" r:id="rId19" tooltip="Jofra Archer" display="https://www.espncricinfo.com/cricketers/jofra-archer-669855" xr:uid="{62C401A7-6AA6-4F4B-85B3-03A177A26003}"/>
+    <hyperlink ref="B29" r:id="rId20" tooltip="RR" display="https://www.espncricinfo.com/team/rajasthan-royals-335977" xr:uid="{E797109F-DB24-4824-8869-295CC7A1CC0D}"/>
+    <hyperlink ref="A34" r:id="rId21" tooltip="Virat Kohli" display="https://www.espncricinfo.com/cricketers/virat-kohli-253802" xr:uid="{393F9769-BF04-411A-B7CC-261C97E912C2}"/>
+    <hyperlink ref="B32" r:id="rId22" tooltip="RCB" display="https://www.espncricinfo.com/team/royal-challengers-bengaluru-335970" xr:uid="{3E299B96-7998-4CD8-99F2-3747C360228F}"/>
+    <hyperlink ref="A37" r:id="rId23" tooltip="Jamie Overton" display="https://www.espncricinfo.com/cricketers/jamie-overton-510530" xr:uid="{60D080D6-D923-4140-A287-9140D20A7E40}"/>
+    <hyperlink ref="B35" r:id="rId24" tooltip="CSK" display="https://www.espncricinfo.com/team/chennai-super-kings-335974" xr:uid="{9698D00F-8923-4F71-841F-E91B1B146F86}"/>
+    <hyperlink ref="A40" r:id="rId25" tooltip="Kartik Tyagi" display="https://www.espncricinfo.com/cricketers/kartik-tyagi-1122918" xr:uid="{85A88857-355E-4365-AA11-243D39F3FD09}"/>
+    <hyperlink ref="B38" r:id="rId26" tooltip="KKR" display="https://www.espncricinfo.com/team/kolkata-knight-riders-335971" xr:uid="{7D3ECB9F-2F8B-40E9-8115-B928FC4BB3E4}"/>
+    <hyperlink ref="A43" r:id="rId27" tooltip="Romario Shepherd" display="https://www.espncricinfo.com/cricketers/romario-shepherd-677077" xr:uid="{7341833F-E0A7-4EB3-9E18-FACD24AD63C3}"/>
+    <hyperlink ref="B41" r:id="rId28" tooltip="RCB" display="https://www.espncricinfo.com/team/royal-challengers-bengaluru-335970" xr:uid="{6AA2C5F3-0719-4434-9F89-E9646E5793B0}"/>
+    <hyperlink ref="A46" r:id="rId29" tooltip="Ajinkya Rahane" display="https://www.espncricinfo.com/cricketers/ajinkya-rahane-277916" xr:uid="{1A3EEB86-0B85-4717-8689-19CEAC3F08C8}"/>
+    <hyperlink ref="B44" r:id="rId30" tooltip="KKR" display="https://www.espncricinfo.com/team/kolkata-knight-riders-335971" xr:uid="{16F6EE1C-5A79-4BFF-B633-3223B9D416EE}"/>
+    <hyperlink ref="A49" r:id="rId31" tooltip="Finn Allen" display="https://www.espncricinfo.com/cricketers/finn-allen-959759" xr:uid="{8A1CEFF0-0241-4E71-8594-5939F5759D3C}"/>
+    <hyperlink ref="B47" r:id="rId32" tooltip="KKR" display="https://www.espncricinfo.com/team/kolkata-knight-riders-335971" xr:uid="{032997F3-3D5F-488A-B443-40740B50389C}"/>
+    <hyperlink ref="A52" r:id="rId33" tooltip="Ravindra Jadeja" display="https://www.espncricinfo.com/cricketers/ravindra-jadeja-234675" xr:uid="{8DA617EB-E91A-413A-A605-56A38AAAB43B}"/>
+    <hyperlink ref="B50" r:id="rId34" tooltip="RR" display="https://www.espncricinfo.com/team/rajasthan-royals-335977" xr:uid="{CEA6C799-6F12-4DD3-A1F0-1ED6169EFF4A}"/>
+    <hyperlink ref="A55" r:id="rId35" tooltip="Jaydev Unadkat" display="https://www.espncricinfo.com/cricketers/jaydev-unadkat-390484" xr:uid="{9BCE98E8-1B3F-46E0-B302-C0217593D4B2}"/>
+    <hyperlink ref="B53" r:id="rId36" tooltip="SRH" display="https://www.espncricinfo.com/team/sunrisers-hyderabad-628333" xr:uid="{3D142B1F-4D8B-473F-BF3F-7C85A0150491}"/>
+    <hyperlink ref="A58" r:id="rId37" tooltip="Suyash Sharma" display="https://www.espncricinfo.com/cricketers/suyash-sharma-1350792" xr:uid="{6BEA5905-F258-417D-B386-52AAA55DCF68}"/>
+    <hyperlink ref="B56" r:id="rId38" tooltip="RCB" display="https://www.espncricinfo.com/team/royal-challengers-bengaluru-335970" xr:uid="{048B4CE6-AAF8-401F-9C56-86DD59753171}"/>
+    <hyperlink ref="A61" r:id="rId39" tooltip="Angkrish Raghuvanshi" display="https://www.espncricinfo.com/cricketers/angkrish-raghuvanshi-1292495" xr:uid="{69CA0AA5-0237-42B2-A5A7-71D5583C9781}"/>
+    <hyperlink ref="B59" r:id="rId40" tooltip="KKR" display="https://www.espncricinfo.com/team/kolkata-knight-riders-335971" xr:uid="{074C08DE-168A-4445-9487-E394D693D42E}"/>
+    <hyperlink ref="A64" r:id="rId41" tooltip="Hardik Pandya" display="https://www.espncricinfo.com/cricketers/hardik-pandya-625371" xr:uid="{921FFA03-A0DB-44FB-ADC0-606ADAFAB656}"/>
+    <hyperlink ref="B62" r:id="rId42" tooltip="MI" display="https://www.espncricinfo.com/team/mumbai-indians-335978" xr:uid="{E6A4A964-E5F1-4F62-8239-5F3F6E97CCB4}"/>
+    <hyperlink ref="A67" r:id="rId43" tooltip="Bhuvneshwar Kumar" display="https://www.espncricinfo.com/cricketers/bhuvneshwar-kumar-326016" xr:uid="{C05A388F-3B11-4C19-9AC3-448D60AC9905}"/>
+    <hyperlink ref="B65" r:id="rId44" tooltip="RCB" display="https://www.espncricinfo.com/team/royal-challengers-bengaluru-335970" xr:uid="{7F92ECEF-7E7D-4591-8538-35297EFBF8F8}"/>
+    <hyperlink ref="A70" r:id="rId45" tooltip="David Payne" display="https://www.espncricinfo.com/cricketers/david-payne-362710" xr:uid="{52F65793-3F5D-406F-ACD5-89165E9BE00C}"/>
+    <hyperlink ref="B68" r:id="rId46" tooltip="SRH" display="https://www.espncricinfo.com/team/sunrisers-hyderabad-628333" xr:uid="{146927FB-C980-4AE7-8925-EE92798C501F}"/>
+    <hyperlink ref="A73" r:id="rId47" tooltip="Jasprit Bumrah" display="https://www.espncricinfo.com/cricketers/jasprit-bumrah-625383" xr:uid="{B1F049D2-2AD2-484E-857A-65D78D184F97}"/>
+    <hyperlink ref="B71" r:id="rId48" tooltip="MI" display="https://www.espncricinfo.com/team/mumbai-indians-335978" xr:uid="{9375B5C4-0EBE-48EF-8FA1-C992A013605D}"/>
+    <hyperlink ref="A76" r:id="rId49" tooltip="Vaibhav Arora" display="https://www.espncricinfo.com/cricketers/vaibhav-arora-1209292" xr:uid="{8B98709F-33F7-450C-832D-D67E31A7C7D5}"/>
+    <hyperlink ref="B74" r:id="rId50" tooltip="KKR" display="https://www.espncricinfo.com/team/kolkata-knight-riders-335971" xr:uid="{CD832A2A-FD31-4B51-9579-17E3471C5714}"/>
+    <hyperlink ref="A79" r:id="rId51" tooltip="Sunil Narine" display="https://www.espncricinfo.com/cricketers/sunil-narine-230558" xr:uid="{D50439B2-9A49-40A1-9BEB-9A938B099D4F}"/>
+    <hyperlink ref="B77" r:id="rId52" tooltip="KKR" display="https://www.espncricinfo.com/team/kolkata-knight-riders-335971" xr:uid="{4B4A927B-2489-4817-B0C9-B2C6DE8D1A8D}"/>
+    <hyperlink ref="A82" r:id="rId53" tooltip="Rajat Patidar" display="https://www.espncricinfo.com/cricketers/rajat-patidar-823703" xr:uid="{A383D355-4A3F-4113-9C41-299B965A1C79}"/>
+    <hyperlink ref="B80" r:id="rId54" tooltip="RCB" display="https://www.espncricinfo.com/team/royal-challengers-bengaluru-335970" xr:uid="{E4A31091-BCF5-4FFA-B5CB-9AD7CA2CDC32}"/>
+    <hyperlink ref="A85" r:id="rId55" tooltip="Kartik Sharma" display="https://www.espncricinfo.com/cricketers/kartik-sharma-1459392" xr:uid="{A0777372-9E47-4474-A59C-B87B6640CA98}"/>
+    <hyperlink ref="B83" r:id="rId56" tooltip="CSK" display="https://www.espncricinfo.com/team/chennai-super-kings-335974" xr:uid="{0A39F81C-B0A5-4E34-ABAA-4F6A108BA184}"/>
+    <hyperlink ref="A88" r:id="rId57" tooltip="Sandeep Sharma" display="https://www.espncricinfo.com/cricketers/sandeep-sharma-438362" xr:uid="{4730967D-156D-473D-AE50-FAAA48433937}"/>
+    <hyperlink ref="B86" r:id="rId58" tooltip="RR" display="https://www.espncricinfo.com/team/rajasthan-royals-335977" xr:uid="{9D7861E7-979F-48FC-B25C-D136FE7B0124}"/>
+    <hyperlink ref="A91" r:id="rId59" tooltip="Harsh Dubey" display="https://www.espncricinfo.com/cricketers/harsh-dubey-1216159" xr:uid="{D0F8C62D-38DA-409D-A588-E33C3AD57448}"/>
+    <hyperlink ref="B89" r:id="rId60" tooltip="SRH" display="https://www.espncricinfo.com/team/sunrisers-hyderabad-628333" xr:uid="{067484E3-F377-4637-867C-040DA8899468}"/>
+    <hyperlink ref="A94" r:id="rId61" tooltip="Yashasvi Jaiswal" display="https://www.espncricinfo.com/cricketers/yashasvi-jaiswal-1151278" xr:uid="{EB681B1C-0ABB-4082-8F75-A12E2688860D}"/>
+    <hyperlink ref="B92" r:id="rId62" tooltip="RR" display="https://www.espncricinfo.com/team/rajasthan-royals-335977" xr:uid="{7782BCC9-1340-4824-93FA-6D26F223FE61}"/>
+    <hyperlink ref="A97" r:id="rId63" tooltip="Sarfaraz Khan" display="https://www.espncricinfo.com/cricketers/sarfaraz-khan-642525" xr:uid="{C8E752AB-0DF2-4916-9CCF-9B6B22405708}"/>
+    <hyperlink ref="B95" r:id="rId64" tooltip="CSK" display="https://www.espncricinfo.com/team/chennai-super-kings-335974" xr:uid="{F224AB36-3CC8-44B8-9AF4-7A18F4DC08AF}"/>
+    <hyperlink ref="A100" r:id="rId65" tooltip="Trent Boult" display="https://www.espncricinfo.com/cricketers/trent-boult-277912" xr:uid="{05187FC7-856B-4AFD-8844-B6FCFF26470E}"/>
+    <hyperlink ref="B98" r:id="rId66" tooltip="MI" display="https://www.espncricinfo.com/team/mumbai-indians-335978" xr:uid="{9CB79093-C4A7-478B-A4CB-2D2D26A8BAFA}"/>
+    <hyperlink ref="A103" r:id="rId67" tooltip="Anshul Kamboj" display="https://www.espncricinfo.com/cricketers/anshul-kamboj-1175428" xr:uid="{08120728-1F8A-435A-91FA-E044F46E9327}"/>
+    <hyperlink ref="B101" r:id="rId68" tooltip="CSK" display="https://www.espncricinfo.com/team/chennai-super-kings-335974" xr:uid="{A6CAD386-315F-44C4-B374-488C29761B1D}"/>
+    <hyperlink ref="A106" r:id="rId69" tooltip="Brijesh Sharma" display="https://www.espncricinfo.com/cricketers/brijesh-sharma-1515046" xr:uid="{E608E085-A601-4C0B-AAA4-99CFF4DBE521}"/>
+    <hyperlink ref="B104" r:id="rId70" tooltip="RR" display="https://www.espncricinfo.com/team/rajasthan-royals-335977" xr:uid="{A409B975-B4C2-430B-ACB4-30B501D227D6}"/>
+    <hyperlink ref="A109" r:id="rId71" tooltip="Abhinandan Singh" display="https://www.espncricinfo.com/cricketers/abhinandan-singh-1449085" xr:uid="{4BA64F72-5460-4744-A4A6-6A72347ABA95}"/>
+    <hyperlink ref="B107" r:id="rId72" tooltip="RCB" display="https://www.espncricinfo.com/team/royal-challengers-bengaluru-335970" xr:uid="{93BB3677-D0E4-4681-B467-A6B1D6A9C35D}"/>
+    <hyperlink ref="A112" r:id="rId73" tooltip="Suryakumar Yadav" display="https://www.espncricinfo.com/cricketers/suryakumar-yadav-446507" xr:uid="{CBDEA447-36D9-4CDE-A376-AB0F9B55157D}"/>
+    <hyperlink ref="B110" r:id="rId74" tooltip="MI" display="https://www.espncricinfo.com/team/mumbai-indians-335978" xr:uid="{422AAA32-9651-4245-907A-53CC05FB55F9}"/>
+    <hyperlink ref="A115" r:id="rId75" tooltip="Heinrich Klaasen" display="https://www.espncricinfo.com/cricketers/heinrich-klaasen-436757" xr:uid="{5F54A73A-97B0-45AF-B6C0-FE87B008693D}"/>
+    <hyperlink ref="B113" r:id="rId76" tooltip="SRH" display="https://www.espncricinfo.com/team/sunrisers-hyderabad-628333" xr:uid="{FD9814AB-0E33-4B64-AEF3-B5EA3DF744B4}"/>
+    <hyperlink ref="A118" r:id="rId77" tooltip="Dhruv Jurel" display="https://www.espncricinfo.com/cricketers/dhruv-jurel-1175488" xr:uid="{C93400AC-668E-4555-B23C-128BDE2B4C0E}"/>
+    <hyperlink ref="B116" r:id="rId78" tooltip="RR" display="https://www.espncricinfo.com/team/rajasthan-royals-335977" xr:uid="{EC1FBE55-FC8D-4A70-B48D-3A8D2B7106E4}"/>
+    <hyperlink ref="A121" r:id="rId79" tooltip="Tilak Varma" display="https://www.espncricinfo.com/cricketers/tilak-varma-1170265" xr:uid="{58895111-5EB2-468A-BA95-768853A33CDB}"/>
+    <hyperlink ref="B119" r:id="rId80" tooltip="MI" display="https://www.espncricinfo.com/team/mumbai-indians-335978" xr:uid="{EA57B348-9978-4F57-ADB8-8489A454501B}"/>
+    <hyperlink ref="A124" r:id="rId81" tooltip="Cameron Green" display="https://www.espncricinfo.com/cricketers/cameron-green-1076713" xr:uid="{CA4534FC-941A-4924-B293-CAF84C13777C}"/>
+    <hyperlink ref="B122" r:id="rId82" tooltip="KKR" display="https://www.espncricinfo.com/team/kolkata-knight-riders-335971" xr:uid="{3FD06809-12C3-473F-B5BB-C3120FE08FF7}"/>
+    <hyperlink ref="A127" r:id="rId83" tooltip="Ravi Bishnoi" display="https://www.espncricinfo.com/cricketers/ravi-bishnoi-1175441" xr:uid="{3F8AF451-C1E5-419C-8464-A32B4A6C6A0C}"/>
+    <hyperlink ref="B125" r:id="rId84" tooltip="RR" display="https://www.espncricinfo.com/team/rajasthan-royals-335977" xr:uid="{070A7806-D7A9-45EE-B68B-362BCE90065A}"/>
+    <hyperlink ref="A130" r:id="rId85" tooltip="Shivam Dube" display="https://www.espncricinfo.com/cricketers/shivam-dube-714451" xr:uid="{5A4A3493-FFF9-4842-A870-D82251B66B0C}"/>
+    <hyperlink ref="B128" r:id="rId86" tooltip="CSK" display="https://www.espncricinfo.com/team/chennai-super-kings-335974" xr:uid="{FA79142D-C4BD-4F83-AE0D-A4CE143E0236}"/>
+    <hyperlink ref="A133" r:id="rId87" tooltip="Tim David" display="https://www.espncricinfo.com/cricketers/tim-david-892749" xr:uid="{A9B8BEE1-307D-41C4-8C8F-9D55B4CC4AEE}"/>
+    <hyperlink ref="B131" r:id="rId88" tooltip="RCB" display="https://www.espncricinfo.com/team/royal-challengers-bengaluru-335970" xr:uid="{018E552C-AA6E-4721-AAA4-FC10B702A54F}"/>
+    <hyperlink ref="A136" r:id="rId89" tooltip="Riyan Parag" display="https://www.espncricinfo.com/cricketers/riyan-parag-1079434" xr:uid="{42719518-2AD6-4D32-B9C5-739515AE24C2}"/>
+    <hyperlink ref="B134" r:id="rId90" tooltip="RR" display="https://www.espncricinfo.com/team/rajasthan-royals-335977" xr:uid="{F3131DF4-C6EB-4247-B939-98A3EB49170A}"/>
+    <hyperlink ref="A139" r:id="rId91" tooltip="Khaleel Ahmed" display="https://www.espncricinfo.com/cricketers/khaleel-ahmed-942645" xr:uid="{C4C67E09-8BAC-4985-830D-8BE253176FB2}"/>
+    <hyperlink ref="B137" r:id="rId92" tooltip="CSK" display="https://www.espncricinfo.com/team/chennai-super-kings-335974" xr:uid="{0ABA35F3-E0D0-4C8B-B2CE-B8AB9596630A}"/>
+    <hyperlink ref="A142" r:id="rId93" tooltip="Blessing Muzarabani" display="https://www.espncricinfo.com/cricketers/blessing-muzarabani-827051" xr:uid="{9517E67B-9BA6-47E5-9939-664999E1BC18}"/>
+    <hyperlink ref="B140" r:id="rId94" tooltip="KKR" display="https://www.espncricinfo.com/team/kolkata-knight-riders-335971" xr:uid="{3FB66825-D04C-4451-935E-C06CAFFC26BD}"/>
+    <hyperlink ref="A145" r:id="rId95" tooltip="Rinku Singh" display="https://www.espncricinfo.com/cricketers/rinku-singh-723105" xr:uid="{6C08D272-1A3F-4FE2-9D2A-5161DC28F7E1}"/>
+    <hyperlink ref="B143" r:id="rId96" tooltip="KKR" display="https://www.espncricinfo.com/team/kolkata-knight-riders-335971" xr:uid="{DA9FCAD8-774C-429F-AF84-A22EC0CF9CE4}"/>
+    <hyperlink ref="A148" r:id="rId97" tooltip="Varun Chakravarthy" display="https://www.espncricinfo.com/cricketers/varun-chakravarthy-1108375" xr:uid="{DB6F274A-CC6D-4508-ACA1-128DA47143AA}"/>
+    <hyperlink ref="B146" r:id="rId98" tooltip="KKR" display="https://www.espncricinfo.com/team/kolkata-knight-riders-335971" xr:uid="{6EBBE013-AFB0-4095-ADA4-6A9D0E4B98E7}"/>
+    <hyperlink ref="A151" r:id="rId99" tooltip="Salil Arora" display="https://www.espncricinfo.com/cricketers/salil-arora-1199281" xr:uid="{1BB0118F-D70A-4C06-8614-84F422D15AAC}"/>
+    <hyperlink ref="B149" r:id="rId100" tooltip="SRH" display="https://www.espncricinfo.com/team/sunrisers-hyderabad-628333" xr:uid="{57927B5D-7EE8-4CD5-AC62-B70483EEC1B0}"/>
+    <hyperlink ref="A154" r:id="rId101" tooltip="Naman Dhir" display="https://www.espncricinfo.com/cricketers/naman-dhir-1287032" xr:uid="{DA0EDEF7-44A6-42F8-814F-9EF754DFC3FD}"/>
+    <hyperlink ref="B152" r:id="rId102" tooltip="MI" display="https://www.espncricinfo.com/team/mumbai-indians-335978" xr:uid="{B9DD7357-3E99-4618-B62B-847A1ABDB310}"/>
+    <hyperlink ref="A157" r:id="rId103" tooltip="Travis Head" display="https://www.espncricinfo.com/cricketers/travis-head-530011" xr:uid="{E50721FF-E5B4-44F2-9769-CC7AD2E33C31}"/>
+    <hyperlink ref="B155" r:id="rId104" tooltip="SRH" display="https://www.espncricinfo.com/team/sunrisers-hyderabad-628333" xr:uid="{DA33E996-E103-4C79-A318-8DEE0E6A7CF8}"/>
+    <hyperlink ref="A160" r:id="rId105" tooltip="Anukul Roy" display="https://www.espncricinfo.com/cricketers/anukul-roy-1079839" xr:uid="{D9D66CEE-E59F-42C4-A32A-23463A44BCA7}"/>
+    <hyperlink ref="B158" r:id="rId106" tooltip="KKR" display="https://www.espncricinfo.com/team/kolkata-knight-riders-335971" xr:uid="{C23E56EF-99DD-489F-8137-3BBFAF9EA297}"/>
+    <hyperlink ref="A163" r:id="rId107" tooltip="Sanju Samson" display="https://www.espncricinfo.com/cricketers/sanju-samson-425943" xr:uid="{2BA19747-3D2B-4226-BC97-6E5D2788E726}"/>
+    <hyperlink ref="B161" r:id="rId108" tooltip="CSK" display="https://www.espncricinfo.com/team/chennai-super-kings-335974" xr:uid="{A01478E2-CEFF-4CDD-8817-85FA1692CE34}"/>
+    <hyperlink ref="A166" r:id="rId109" tooltip="AM Ghazanfar" display="https://www.espncricinfo.com/cricketers/am-ghazanfar-1326798" xr:uid="{02CCBBF7-A759-4828-A563-52C9C2647CC0}"/>
+    <hyperlink ref="B164" r:id="rId110" tooltip="MI" display="https://www.espncricinfo.com/team/mumbai-indians-335978" xr:uid="{ABA592E2-E685-470E-BC7C-2CFA7D68D8B0}"/>
+    <hyperlink ref="A169" r:id="rId111" tooltip="Phil Salt" display="https://www.espncricinfo.com/cricketers/phil-salt-669365" xr:uid="{53338FAE-C342-4D9D-9DE8-592ED6DDDC86}"/>
+    <hyperlink ref="B167" r:id="rId112" tooltip="RCB" display="https://www.espncricinfo.com/team/royal-challengers-bengaluru-335970" xr:uid="{59E2225F-00E0-4BB0-986D-362A1FBDB053}"/>
+    <hyperlink ref="A172" r:id="rId113" tooltip="Sherfane Rutherford" display="https://www.espncricinfo.com/cricketers/sherfane-rutherford-914541" xr:uid="{B9ED47B3-5179-4310-BA1C-483AE7D61C00}"/>
+    <hyperlink ref="B170" r:id="rId114" tooltip="MI" display="https://www.espncricinfo.com/team/mumbai-indians-335978" xr:uid="{9698791E-F64A-46FF-813D-BE25EEBBC254}"/>
+    <hyperlink ref="A175" r:id="rId115" tooltip="Shimron Hetmyer" display="https://www.espncricinfo.com/cricketers/shimron-hetmyer-670025" xr:uid="{52EFFC4C-84F0-4DC6-8FA4-38D428DA10E6}"/>
+    <hyperlink ref="B173" r:id="rId116" tooltip="RR" display="https://www.espncricinfo.com/team/rajasthan-royals-335977" xr:uid="{493C0736-B9C5-4978-B316-87084B50AE21}"/>
+    <hyperlink ref="A178" r:id="rId117" tooltip="Krunal Pandya" display="https://www.espncricinfo.com/cricketers/krunal-pandya-471342" xr:uid="{D25A2168-103D-49C6-875D-ED53A790763A}"/>
+    <hyperlink ref="B176" r:id="rId118" tooltip="RCB" display="https://www.espncricinfo.com/team/royal-challengers-bengaluru-335970" xr:uid="{EB3C420D-BE93-46CD-870D-5B4467A58B57}"/>
+    <hyperlink ref="A181" r:id="rId119" tooltip="Jitesh Sharma" display="https://www.espncricinfo.com/cricketers/jitesh-sharma-721867" xr:uid="{D9B639EC-45C9-40B5-99CF-FB570DB9817D}"/>
+    <hyperlink ref="B179" r:id="rId120" tooltip="RCB" display="https://www.espncricinfo.com/team/royal-challengers-bengaluru-335970" xr:uid="{FEB18DEC-CC1C-457B-B25D-227C28DB7F7C}"/>
+    <hyperlink ref="A184" r:id="rId121" tooltip="Ayush Mhatre" display="https://www.espncricinfo.com/cricketers/ayush-mhatre-1452455" xr:uid="{65A6A2BD-917C-41E5-B54E-E3604EFD9DA5}"/>
+    <hyperlink ref="B182" r:id="rId122" tooltip="CSK" display="https://www.espncricinfo.com/team/chennai-super-kings-335974" xr:uid="{958A8ADE-6DF5-4AFB-AD82-B1754CD8D51F}"/>
+    <hyperlink ref="A187" r:id="rId123" tooltip="Harshal Patel" display="https://www.espncricinfo.com/cricketers/harshal-patel-390481" xr:uid="{8F10AA2C-4C58-487E-9D2F-32B067C7EFCE}"/>
+    <hyperlink ref="B185" r:id="rId124" tooltip="SRH" display="https://www.espncricinfo.com/team/sunrisers-hyderabad-628333" xr:uid="{223E6993-81EF-45EA-BC65-F2FB10701390}"/>
+    <hyperlink ref="A190" r:id="rId125" tooltip="Ruturaj Gaikwad" display="https://www.espncricinfo.com/cricketers/ruturaj-gaikwad-1060380" xr:uid="{FC173D28-4856-490B-BB76-DCAA831A1A59}"/>
+    <hyperlink ref="B188" r:id="rId126" tooltip="CSK" display="https://www.espncricinfo.com/team/chennai-super-kings-335974" xr:uid="{3C2EBB97-F3A0-4F4B-8FAF-307EFAFEFFB9}"/>
+    <hyperlink ref="A193" r:id="rId127" tooltip="Mayank Markande" display="https://www.espncricinfo.com/cricketers/mayank-markande-1081442" xr:uid="{2E5CD6B1-6908-47C4-BC05-0104592F560A}"/>
+    <hyperlink ref="B191" r:id="rId128" tooltip="MI" display="https://www.espncricinfo.com/team/mumbai-indians-335978" xr:uid="{0FFC991F-7DFA-4DEB-A496-74C7F549DE7F}"/>
+    <hyperlink ref="A196" r:id="rId129" tooltip="Abhishek Sharma" display="https://www.espncricinfo.com/cricketers/abhishek-sharma-1070183" xr:uid="{DC033821-361A-48BD-8880-AC2122660C68}"/>
+    <hyperlink ref="B194" r:id="rId130" tooltip="SRH" display="https://www.espncricinfo.com/team/sunrisers-hyderabad-628333" xr:uid="{7DF186E6-1643-4930-A1BE-076B020F40B1}"/>
+    <hyperlink ref="A199" r:id="rId131" tooltip="Ramandeep Singh" display="https://www.espncricinfo.com/cricketers/ramandeep-singh-1079470" xr:uid="{7C55E9DB-8C6A-4FBB-8653-E60674299E8B}"/>
+    <hyperlink ref="B197" r:id="rId132" tooltip="KKR" display="https://www.espncricinfo.com/team/kolkata-knight-riders-335971" xr:uid="{1F8379C7-3FBF-425B-A8FB-DFCF2E7015B1}"/>
+    <hyperlink ref="A202" r:id="rId133" tooltip="Matthew Short" display="https://www.espncricinfo.com/cricketers/matthew-short-605575" xr:uid="{3DEB4F92-E943-477E-9531-D09BF35EA7F0}"/>
+    <hyperlink ref="B200" r:id="rId134" tooltip="CSK" display="https://www.espncricinfo.com/team/chennai-super-kings-335974" xr:uid="{CC0A25B9-D6FD-4B65-9800-C153031BF430}"/>
+    <hyperlink ref="A205" r:id="rId135" tooltip="Nitish Kumar Reddy" display="https://www.espncricinfo.com/cricketers/nitish-kumar-reddy-1175496" xr:uid="{DD270F12-7E16-44B0-ABD5-F779FB535780}"/>
+    <hyperlink ref="B203" r:id="rId136" tooltip="SRH" display="https://www.espncricinfo.com/team/sunrisers-hyderabad-628333" xr:uid="{140E2AA9-F366-46DF-B389-602C8C0AC55E}"/>
+    <hyperlink ref="A208" r:id="rId137" tooltip="Eshan Malinga" display="https://www.espncricinfo.com/cricketers/eshan-malinga-1306214" xr:uid="{72EE0C2A-1EDF-4A2B-8C0A-29787418E148}"/>
+    <hyperlink ref="B206" r:id="rId138" tooltip="SRH" display="https://www.espncricinfo.com/team/sunrisers-hyderabad-628333" xr:uid="{B632D798-8987-4A1C-9F78-4CE0E23B6529}"/>
+    <hyperlink ref="A211" r:id="rId139" tooltip="Noor Ahmad" display="https://www.espncricinfo.com/cricketers/noor-ahmad-1182529" xr:uid="{3255C33D-25A7-41D7-B0E4-AB1F06D307A0}"/>
+    <hyperlink ref="B209" r:id="rId140" tooltip="CSK" display="https://www.espncricinfo.com/team/chennai-super-kings-335974" xr:uid="{B866803C-0296-45DE-A179-F265666FB13C}"/>
+    <hyperlink ref="A214" r:id="rId141" tooltip="Matt Henry" display="https://www.espncricinfo.com/cricketers/matt-henry-506612" xr:uid="{DFA7AA3B-6701-4664-89D9-4285F9ECD64C}"/>
+    <hyperlink ref="B212" r:id="rId142" tooltip="CSK" display="https://www.espncricinfo.com/team/chennai-super-kings-335974" xr:uid="{9D3EADB2-388F-4EF5-86AE-7D5B0202AE4B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId97"/>
+  <drawing r:id="rId143"/>
 </worksheet>
 </file>